--- a/data/proteomics/membrance_size_across_compartment.xlsx
+++ b/data/proteomics/membrance_size_across_compartment.xlsx
@@ -1,77 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/xluhon/Documents/GitHub/De-nevo-protein-3D-structure-yeast/data/proteomics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F893791D-E589-B045-A90C-E902E4491AB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2019C32C-BDEE-314E-9D22-28E7AF8B0E06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29220" yWindow="500" windowWidth="32500" windowHeight="16940" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="26880" windowHeight="15220" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="6" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="7" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="8" r:id="rId5"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet3!$A$2:$A$77</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet3!$C$1</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">Sheet3!$E$2:$E$139</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">Sheet3!$A$2:$A$77</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">Sheet3!$C$1</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">Sheet3!$C$2:$C$77</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">Sheet3!$E$1</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">Sheet3!$E$2:$E$77</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">Sheet3!$A$2:$A$77</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">Sheet3!$C$1</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">Sheet3!$C$2:$C$77</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">Sheet3!$E$1</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet3!$C$2:$C$77</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">Sheet3!$E$2:$E$77</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">Sheet3!$A$1</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">Sheet3!$A$2:$A$139</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">Sheet3!$C$1</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">Sheet3!$C$2:$C$139</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">Sheet3!$E$1</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">Sheet3!$E$2:$E$139</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">Sheet3!$A$1</definedName>
-    <definedName name="_xlchart.v1.28" hidden="1">Sheet3!$A$2:$A$139</definedName>
-    <definedName name="_xlchart.v1.29" hidden="1">Sheet3!$C$1</definedName>
-    <definedName name="_xlchart.v1.3" hidden="1">Sheet3!$E$1</definedName>
-    <definedName name="_xlchart.v1.30" hidden="1">Sheet3!$C$2:$C$139</definedName>
-    <definedName name="_xlchart.v1.31" hidden="1">Sheet3!$E$1</definedName>
-    <definedName name="_xlchart.v1.32" hidden="1">Sheet3!$E$2:$E$139</definedName>
-    <definedName name="_xlchart.v1.33" hidden="1">Sheet3!$A$2:$A$77</definedName>
-    <definedName name="_xlchart.v1.34" hidden="1">Sheet3!$C$1</definedName>
-    <definedName name="_xlchart.v1.35" hidden="1">Sheet3!$C$2:$C$77</definedName>
-    <definedName name="_xlchart.v1.36" hidden="1">Sheet3!$E$1</definedName>
-    <definedName name="_xlchart.v1.37" hidden="1">Sheet3!$E$2:$E$77</definedName>
-    <definedName name="_xlchart.v1.38" hidden="1">Sheet3!$A$2:$A$77</definedName>
-    <definedName name="_xlchart.v1.39" hidden="1">Sheet3!$C$1</definedName>
-    <definedName name="_xlchart.v1.4" hidden="1">Sheet3!$E$2:$E$77</definedName>
-    <definedName name="_xlchart.v1.40" hidden="1">Sheet3!$C$2:$C$77</definedName>
-    <definedName name="_xlchart.v1.41" hidden="1">Sheet3!$E$1</definedName>
-    <definedName name="_xlchart.v1.42" hidden="1">Sheet3!$E$2:$E$77</definedName>
-    <definedName name="_xlchart.v1.43" hidden="1">Sheet3!$A$2:$A$77</definedName>
-    <definedName name="_xlchart.v1.44" hidden="1">Sheet3!$C$1</definedName>
-    <definedName name="_xlchart.v1.45" hidden="1">Sheet3!$C$2:$C$77</definedName>
-    <definedName name="_xlchart.v1.46" hidden="1">Sheet3!$E$1</definedName>
-    <definedName name="_xlchart.v1.47" hidden="1">Sheet3!$E$2:$E$77</definedName>
-    <definedName name="_xlchart.v1.48" hidden="1">Sheet3!$A$2:$A$77</definedName>
-    <definedName name="_xlchart.v1.49" hidden="1">Sheet3!$C$1</definedName>
-    <definedName name="_xlchart.v1.5" hidden="1">Sheet3!$A$1</definedName>
-    <definedName name="_xlchart.v1.50" hidden="1">Sheet3!$C$2:$C$77</definedName>
-    <definedName name="_xlchart.v1.51" hidden="1">Sheet3!$E$1</definedName>
-    <definedName name="_xlchart.v1.52" hidden="1">Sheet3!$E$2:$E$77</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">Sheet3!$A$2:$A$139</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">Sheet3!$C$1</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">Sheet3!$C$2:$C$139</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">Sheet3!$E$1</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -86,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="258">
   <si>
     <t>compartment</t>
   </si>
@@ -753,12 +700,120 @@
   <si>
     <t>mitochondrial outer membrane_M</t>
   </si>
+  <si>
+    <t>kinetic</t>
+  </si>
+  <si>
+    <t>dilution rate (/h)</t>
+  </si>
+  <si>
+    <t>qGlucose (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qNH4 (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qGln (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qPhe (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qIle (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qNitrogen (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qEtOH (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qAce (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qPyr (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qSuc (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qGlycerol (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qCO2 (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>qO2 (mmol/gDW h)</t>
+  </si>
+  <si>
+    <t>glucose.H2O concentration (g/L)</t>
+  </si>
+  <si>
+    <t>Nitrogen source</t>
+  </si>
+  <si>
+    <t>nitrogen source concentration (g/L)</t>
+  </si>
+  <si>
+    <t>limiting nutrient</t>
+  </si>
+  <si>
+    <t>C/N ratio</t>
+  </si>
+  <si>
+    <t>experiment subset</t>
+  </si>
+  <si>
+    <t>total RNA content (g/gDW)</t>
+  </si>
+  <si>
+    <t>total protein content (g/gDW)</t>
+  </si>
+  <si>
+    <t>extra notes</t>
+  </si>
+  <si>
+    <t>Ref.</t>
+  </si>
+  <si>
+    <t>NH4</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>GR</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>NM</t>
+  </si>
+  <si>
+    <t>GR, NM</t>
+  </si>
+  <si>
+    <t>Gln</t>
+  </si>
+  <si>
+    <t>labeled "Q" or "Gln"</t>
+  </si>
+  <si>
+    <t>labeled "Q*" or "Gln*"</t>
+  </si>
+  <si>
+    <t>Phe</t>
+  </si>
+  <si>
+    <t>Ile</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -771,8 +826,28 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -788,6 +863,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -827,10 +913,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -859,8 +946,21 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -53310,4 +53410,6532 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5040148-5F5D-D845-BB5E-0A5559FEB9AF}">
+  <dimension ref="A1:AE43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="21.5" customWidth="1"/>
+    <col min="2" max="4" width="28.1640625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="30.1640625" style="12" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" style="12" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="P1" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="V1" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="X1" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="Y1" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="Z1" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="AA1" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="AB1" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="AC1" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="AD1" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="AE1" s="15" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="11">
+        <v>12.220727609623641</v>
+      </c>
+      <c r="C2" s="12">
+        <v>2.884630251876803</v>
+      </c>
+      <c r="D2" s="11">
+        <v>12.62604490502812</v>
+      </c>
+      <c r="E2" s="12">
+        <v>11.392381876000149</v>
+      </c>
+      <c r="F2" s="11">
+        <v>2.4120579177240891</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="H2" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="I2" s="18">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="J2" s="18">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="K2" s="18"/>
+      <c r="L2" s="18"/>
+      <c r="M2" s="18"/>
+      <c r="N2" s="18">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="O2" s="18">
+        <v>0</v>
+      </c>
+      <c r="P2" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="18">
+        <v>7.2308500000000005E-4</v>
+      </c>
+      <c r="R2" s="18">
+        <v>0</v>
+      </c>
+      <c r="S2" s="18">
+        <v>4.0285879999999996E-3</v>
+      </c>
+      <c r="T2" s="18">
+        <v>2.4449999999999998</v>
+      </c>
+      <c r="U2" s="18">
+        <v>2.3620000000000001</v>
+      </c>
+      <c r="V2" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W2" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X2" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y2" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z2" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA2" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB2" s="17">
+        <v>2.1734E-2</v>
+      </c>
+      <c r="AC2" s="17">
+        <v>0.27251471399999999</v>
+      </c>
+      <c r="AD2" s="17"/>
+      <c r="AE2" s="17"/>
+    </row>
+    <row r="3" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="11">
+        <v>12.050687887688911</v>
+      </c>
+      <c r="C3" s="12">
+        <v>2.6485201917393981</v>
+      </c>
+      <c r="D3" s="11">
+        <v>11.296039828454891</v>
+      </c>
+      <c r="E3" s="12">
+        <v>10.119578978588279</v>
+      </c>
+      <c r="F3" s="11">
+        <v>2.232089730391285</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="I3" s="18">
+        <v>0.70399999999999996</v>
+      </c>
+      <c r="J3" s="18">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="O3" s="18">
+        <v>0</v>
+      </c>
+      <c r="P3" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="18">
+        <v>1.6583900000000001E-4</v>
+      </c>
+      <c r="R3" s="18">
+        <v>0</v>
+      </c>
+      <c r="S3" s="18">
+        <v>6.6796169999999997E-3</v>
+      </c>
+      <c r="T3" s="18">
+        <v>2.105</v>
+      </c>
+      <c r="U3" s="18">
+        <v>2.2759999999999998</v>
+      </c>
+      <c r="V3" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W3" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X3" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y3" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z3" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA3" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB3" s="17">
+        <v>2.4941000000000001E-2</v>
+      </c>
+      <c r="AC3" s="17">
+        <v>0.25082010700000001</v>
+      </c>
+      <c r="AD3" s="17"/>
+      <c r="AE3" s="17"/>
+    </row>
+    <row r="4" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="11">
+        <v>13.78558746427956</v>
+      </c>
+      <c r="C4" s="12">
+        <v>2.693229997986613</v>
+      </c>
+      <c r="D4" s="11">
+        <v>11.706973735523601</v>
+      </c>
+      <c r="E4" s="12">
+        <v>10.566080458762039</v>
+      </c>
+      <c r="F4" s="11">
+        <v>2.2497310200932561</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="H4" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="I4" s="18">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="J4" s="18">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
+      <c r="N4" s="18">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="O4" s="18">
+        <v>0</v>
+      </c>
+      <c r="P4" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="18">
+        <v>3.81541E-4</v>
+      </c>
+      <c r="R4" s="18">
+        <v>0</v>
+      </c>
+      <c r="S4" s="18">
+        <v>9.7823159999999992E-3</v>
+      </c>
+      <c r="T4" s="18">
+        <v>2.383</v>
+      </c>
+      <c r="U4" s="18">
+        <v>1.6240000000000001</v>
+      </c>
+      <c r="V4" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W4" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X4" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y4" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z4" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA4" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB4" s="17">
+        <v>2.5831E-2</v>
+      </c>
+      <c r="AC4" s="17">
+        <v>0.26109650000000001</v>
+      </c>
+      <c r="AD4" s="17"/>
+      <c r="AE4" s="17"/>
+    </row>
+    <row r="5" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="11">
+        <v>15.137462101915849</v>
+      </c>
+      <c r="C5" s="12">
+        <v>4.5640440027735254</v>
+      </c>
+      <c r="D5" s="11">
+        <v>17.39067926677453</v>
+      </c>
+      <c r="E5" s="12">
+        <v>15.95741038094155</v>
+      </c>
+      <c r="F5" s="11">
+        <v>3.8368294719490641</v>
+      </c>
+      <c r="G5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I5" s="18">
+        <v>1.18</v>
+      </c>
+      <c r="J5" s="18">
+        <v>2.2029999999999998</v>
+      </c>
+      <c r="K5" s="18"/>
+      <c r="L5" s="18"/>
+      <c r="M5" s="18"/>
+      <c r="N5" s="18">
+        <v>2.2029999999999998</v>
+      </c>
+      <c r="O5" s="18">
+        <v>0</v>
+      </c>
+      <c r="P5" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="18">
+        <v>1.2795499999999999E-4</v>
+      </c>
+      <c r="R5" s="18">
+        <v>0</v>
+      </c>
+      <c r="S5" s="18">
+        <v>0</v>
+      </c>
+      <c r="T5" s="18">
+        <v>1.93</v>
+      </c>
+      <c r="U5" s="18">
+        <v>2.44</v>
+      </c>
+      <c r="V5" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W5" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X5" s="17">
+        <v>5</v>
+      </c>
+      <c r="Y5" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z5" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA5" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB5" s="17">
+        <v>5.3443999999999998E-2</v>
+      </c>
+      <c r="AC5" s="17">
+        <v>0.35967375000000001</v>
+      </c>
+      <c r="AD5" s="17"/>
+      <c r="AE5" s="17"/>
+    </row>
+    <row r="6" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="11">
+        <v>15.672650812200519</v>
+      </c>
+      <c r="C6" s="12">
+        <v>4.5896366338518542</v>
+      </c>
+      <c r="D6" s="11">
+        <v>17.486556008644719</v>
+      </c>
+      <c r="E6" s="12">
+        <v>15.92402766777022</v>
+      </c>
+      <c r="F6" s="11">
+        <v>3.8657983792716131</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="H6" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I6" s="18">
+        <v>1.127</v>
+      </c>
+      <c r="J6" s="18">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="O6" s="18">
+        <v>1.6766474999999999E-2</v>
+      </c>
+      <c r="P6" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="18">
+        <v>1.5726999999999999E-4</v>
+      </c>
+      <c r="R6" s="18">
+        <v>0</v>
+      </c>
+      <c r="S6" s="18">
+        <v>0</v>
+      </c>
+      <c r="T6" s="18">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="U6" s="18">
+        <v>2.39</v>
+      </c>
+      <c r="V6" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W6" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X6" s="17">
+        <v>5</v>
+      </c>
+      <c r="Y6" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z6" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA6" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB6" s="17">
+        <v>5.0594E-2</v>
+      </c>
+      <c r="AC6" s="17">
+        <v>0.377942893</v>
+      </c>
+      <c r="AD6" s="17"/>
+      <c r="AE6" s="17"/>
+    </row>
+    <row r="7" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="11">
+        <v>13.300694918778969</v>
+      </c>
+      <c r="C7" s="12">
+        <v>3.925821250462723</v>
+      </c>
+      <c r="D7" s="11">
+        <v>17.234771891964989</v>
+      </c>
+      <c r="E7" s="12">
+        <v>15.79116844392064</v>
+      </c>
+      <c r="F7" s="11">
+        <v>3.5122241030300771</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="H7" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="18">
+        <v>1.0980000000000001</v>
+      </c>
+      <c r="J7" s="18">
+        <v>2.0550000000000002</v>
+      </c>
+      <c r="K7" s="18"/>
+      <c r="L7" s="18"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18">
+        <v>2.0550000000000002</v>
+      </c>
+      <c r="O7" s="18">
+        <v>0</v>
+      </c>
+      <c r="P7" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="18">
+        <v>1.3422099999999999E-4</v>
+      </c>
+      <c r="R7" s="18">
+        <v>0</v>
+      </c>
+      <c r="S7" s="18">
+        <v>0</v>
+      </c>
+      <c r="T7" s="18">
+        <v>1.97</v>
+      </c>
+      <c r="U7" s="18">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="V7" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W7" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X7" s="17">
+        <v>5</v>
+      </c>
+      <c r="Y7" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z7" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA7" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB7" s="17">
+        <v>4.5962000000000003E-2</v>
+      </c>
+      <c r="AC7" s="17">
+        <v>0.33645671399999999</v>
+      </c>
+      <c r="AD7" s="17"/>
+      <c r="AE7" s="17"/>
+    </row>
+    <row r="8" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="11">
+        <v>8.4086449588180656</v>
+      </c>
+      <c r="C8" s="12">
+        <v>1.8437941122284061</v>
+      </c>
+      <c r="D8" s="11">
+        <v>12.12206313944575</v>
+      </c>
+      <c r="E8" s="12">
+        <v>11.072965878425141</v>
+      </c>
+      <c r="F8" s="11">
+        <v>1.9131872851569831</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="18">
+        <v>1.51</v>
+      </c>
+      <c r="J8" s="18">
+        <v>0.308</v>
+      </c>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18">
+        <v>0.308</v>
+      </c>
+      <c r="O8" s="18">
+        <v>0</v>
+      </c>
+      <c r="P8" s="18">
+        <v>7.5614127000000003E-2</v>
+      </c>
+      <c r="Q8" s="18">
+        <v>1.7982350000000001E-2</v>
+      </c>
+      <c r="R8" s="18">
+        <v>0</v>
+      </c>
+      <c r="S8" s="18">
+        <v>0</v>
+      </c>
+      <c r="T8" s="18">
+        <v>3.4660000000000002</v>
+      </c>
+      <c r="U8" s="18">
+        <v>3.6160000000000001</v>
+      </c>
+      <c r="V8" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W8" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X8" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y8" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z8" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA8" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB8" s="17">
+        <v>2.2624999999999999E-2</v>
+      </c>
+      <c r="AC8" s="17">
+        <v>0.209333929</v>
+      </c>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="17"/>
+    </row>
+    <row r="9" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="11">
+        <v>9.6533021441943703</v>
+      </c>
+      <c r="C9" s="12">
+        <v>2.0770715761556189</v>
+      </c>
+      <c r="D9" s="11">
+        <v>12.64951553193638</v>
+      </c>
+      <c r="E9" s="12">
+        <v>11.584121402980781</v>
+      </c>
+      <c r="F9" s="11">
+        <v>1.8794210863155849</v>
+      </c>
+      <c r="G9" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I9" s="18">
+        <v>1.5109999999999999</v>
+      </c>
+      <c r="J9" s="18">
+        <v>0.308</v>
+      </c>
+      <c r="K9" s="18"/>
+      <c r="L9" s="18"/>
+      <c r="M9" s="18"/>
+      <c r="N9" s="18">
+        <v>0.308</v>
+      </c>
+      <c r="O9" s="18">
+        <v>0</v>
+      </c>
+      <c r="P9" s="18">
+        <v>4.9087042999999997E-2</v>
+      </c>
+      <c r="Q9" s="18">
+        <v>1.38432E-2</v>
+      </c>
+      <c r="R9" s="18">
+        <v>0</v>
+      </c>
+      <c r="S9" s="18">
+        <v>0</v>
+      </c>
+      <c r="T9" s="18">
+        <v>3.1360000000000001</v>
+      </c>
+      <c r="U9" s="18">
+        <v>3.5219999999999998</v>
+      </c>
+      <c r="V9" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W9" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X9" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y9" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z9" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA9" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB9" s="17">
+        <v>2.6009999999999998E-2</v>
+      </c>
+      <c r="AC9" s="17">
+        <v>0.22151335699999999</v>
+      </c>
+      <c r="AD9" s="17"/>
+      <c r="AE9" s="17"/>
+    </row>
+    <row r="10" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="11">
+        <v>12.032269803669211</v>
+      </c>
+      <c r="C10" s="12">
+        <v>2.653515436727282</v>
+      </c>
+      <c r="D10" s="11">
+        <v>12.848390739933681</v>
+      </c>
+      <c r="E10" s="12">
+        <v>11.49196518969214</v>
+      </c>
+      <c r="F10" s="11">
+        <v>2.0776216004329169</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="18">
+        <v>1.4890000000000001</v>
+      </c>
+      <c r="J10" s="18">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="K10" s="18"/>
+      <c r="L10" s="18"/>
+      <c r="M10" s="18"/>
+      <c r="N10" s="18">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="O10" s="18">
+        <v>0</v>
+      </c>
+      <c r="P10" s="18">
+        <v>6.6037847999999996E-2</v>
+      </c>
+      <c r="Q10" s="18">
+        <v>1.602926E-2</v>
+      </c>
+      <c r="R10" s="18">
+        <v>0</v>
+      </c>
+      <c r="S10" s="18">
+        <v>0</v>
+      </c>
+      <c r="T10" s="18">
+        <v>3.161</v>
+      </c>
+      <c r="U10" s="18">
+        <v>3.8239999999999998</v>
+      </c>
+      <c r="V10" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W10" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X10" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y10" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z10" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA10" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="AB10" s="17">
+        <v>2.7257E-2</v>
+      </c>
+      <c r="AC10" s="17">
+        <v>0.24587221400000001</v>
+      </c>
+      <c r="AD10" s="17"/>
+      <c r="AE10" s="17"/>
+    </row>
+    <row r="11" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="11">
+        <v>13.50925503311483</v>
+      </c>
+      <c r="C11" s="12">
+        <v>3.1150596850078469</v>
+      </c>
+      <c r="D11" s="11">
+        <v>19.213356017144061</v>
+      </c>
+      <c r="E11" s="12">
+        <v>17.760245546638561</v>
+      </c>
+      <c r="F11" s="11">
+        <v>2.855671246618515</v>
+      </c>
+      <c r="G11" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="17">
+        <v>0.13</v>
+      </c>
+      <c r="I11" s="18">
+        <v>2.0190000000000001</v>
+      </c>
+      <c r="J11" s="18">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="O11" s="18">
+        <v>0.14387805000000001</v>
+      </c>
+      <c r="P11" s="18">
+        <v>0.23128044</v>
+      </c>
+      <c r="Q11" s="18">
+        <v>2.4418572999999999E-2</v>
+      </c>
+      <c r="R11" s="18">
+        <v>7.3894399999999995E-4</v>
+      </c>
+      <c r="S11" s="18">
+        <v>4.2122905000000002E-2</v>
+      </c>
+      <c r="T11" s="18">
+        <v>5.51</v>
+      </c>
+      <c r="U11" s="18">
+        <v>5.2519999999999998</v>
+      </c>
+      <c r="V11" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W11" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X11" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y11" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z11" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA11" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB11" s="17">
+        <v>2.6366000000000001E-2</v>
+      </c>
+      <c r="AC11" s="17">
+        <v>0.30372450000000001</v>
+      </c>
+      <c r="AD11" s="17"/>
+      <c r="AE11" s="17"/>
+    </row>
+    <row r="12" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="11">
+        <v>11.51272724725102</v>
+      </c>
+      <c r="C12" s="12">
+        <v>2.5652688123410758</v>
+      </c>
+      <c r="D12" s="11">
+        <v>16.361253031218901</v>
+      </c>
+      <c r="E12" s="12">
+        <v>15.062023396400299</v>
+      </c>
+      <c r="F12" s="11">
+        <v>2.3584391357458778</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="17">
+        <v>0.13</v>
+      </c>
+      <c r="I12" s="18">
+        <v>2.0590000000000002</v>
+      </c>
+      <c r="J12" s="18">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="M12" s="18"/>
+      <c r="N12" s="18">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="O12" s="18">
+        <v>0.13916811300000001</v>
+      </c>
+      <c r="P12" s="18">
+        <v>0.22761730999999999</v>
+      </c>
+      <c r="Q12" s="18">
+        <v>2.5077986E-2</v>
+      </c>
+      <c r="R12" s="18">
+        <v>2.152588E-3</v>
+      </c>
+      <c r="S12" s="18">
+        <v>3.3899711999999999E-2</v>
+      </c>
+      <c r="T12" s="18">
+        <v>5.3739999999999997</v>
+      </c>
+      <c r="U12" s="18">
+        <v>4.5460000000000003</v>
+      </c>
+      <c r="V12" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W12" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X12" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y12" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z12" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA12" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB12" s="17">
+        <v>2.5831E-2</v>
+      </c>
+      <c r="AC12" s="17">
+        <v>0.25690982099999998</v>
+      </c>
+      <c r="AD12" s="17"/>
+      <c r="AE12" s="17"/>
+    </row>
+    <row r="13" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="11">
+        <v>11.253638562470901</v>
+      </c>
+      <c r="C13" s="12">
+        <v>2.6818459667293228</v>
+      </c>
+      <c r="D13" s="11">
+        <v>17.454651562533218</v>
+      </c>
+      <c r="E13" s="12">
+        <v>16.130437578234439</v>
+      </c>
+      <c r="F13" s="11">
+        <v>2.5495242219747771</v>
+      </c>
+      <c r="G13" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0.13</v>
+      </c>
+      <c r="I13" s="18">
+        <v>2.1349999999999998</v>
+      </c>
+      <c r="J13" s="18">
+        <v>0.438</v>
+      </c>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+      <c r="M13" s="18"/>
+      <c r="N13" s="18">
+        <v>0.438</v>
+      </c>
+      <c r="O13" s="18">
+        <v>0.13267562499999999</v>
+      </c>
+      <c r="P13" s="18">
+        <v>0.25727792100000002</v>
+      </c>
+      <c r="Q13" s="18">
+        <v>2.6121129999999999E-2</v>
+      </c>
+      <c r="R13" s="18">
+        <v>0</v>
+      </c>
+      <c r="S13" s="18">
+        <v>4.1071206999999998E-2</v>
+      </c>
+      <c r="T13" s="18">
+        <v>5.3019999999999996</v>
+      </c>
+      <c r="U13" s="18">
+        <v>5.07</v>
+      </c>
+      <c r="V13" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W13" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y13" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z13" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA13" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB13" s="17">
+        <v>2.5297E-2</v>
+      </c>
+      <c r="AC13" s="17">
+        <v>0.26642500000000002</v>
+      </c>
+      <c r="AD13" s="17"/>
+      <c r="AE13" s="17"/>
+    </row>
+    <row r="14" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="11">
+        <v>11.46174857066403</v>
+      </c>
+      <c r="C14" s="12">
+        <v>2.8827272580110348</v>
+      </c>
+      <c r="D14" s="11">
+        <v>19.406955946154611</v>
+      </c>
+      <c r="E14" s="12">
+        <v>17.970587932375171</v>
+      </c>
+      <c r="F14" s="11">
+        <v>2.8600260975894738</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="17">
+        <v>0.18</v>
+      </c>
+      <c r="I14" s="18">
+        <v>3.266</v>
+      </c>
+      <c r="J14" s="18">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+      <c r="M14" s="18"/>
+      <c r="N14" s="18">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="O14" s="18">
+        <v>1.2813869950000001</v>
+      </c>
+      <c r="P14" s="18">
+        <v>0.18048138799999999</v>
+      </c>
+      <c r="Q14" s="18">
+        <v>3.2745818000000003E-2</v>
+      </c>
+      <c r="R14" s="18">
+        <v>0</v>
+      </c>
+      <c r="S14" s="18">
+        <v>5.6452840000000004E-3</v>
+      </c>
+      <c r="T14" s="18">
+        <v>7.2619999999999996</v>
+      </c>
+      <c r="U14" s="18">
+        <v>5.42</v>
+      </c>
+      <c r="V14" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W14" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X14" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y14" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z14" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA14" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB14" s="17">
+        <v>3.9014E-2</v>
+      </c>
+      <c r="AC14" s="17">
+        <v>0.28926142900000001</v>
+      </c>
+      <c r="AD14" s="17"/>
+      <c r="AE14" s="17"/>
+    </row>
+    <row r="15" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="11">
+        <v>10.867314550717889</v>
+      </c>
+      <c r="C15" s="12">
+        <v>2.8444224659559869</v>
+      </c>
+      <c r="D15" s="11">
+        <v>18.608638690749871</v>
+      </c>
+      <c r="E15" s="12">
+        <v>17.19047165069081</v>
+      </c>
+      <c r="F15" s="11">
+        <v>2.6041596717267348</v>
+      </c>
+      <c r="G15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H15" s="17">
+        <v>0.18</v>
+      </c>
+      <c r="I15" s="18">
+        <v>3.202</v>
+      </c>
+      <c r="J15" s="18">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+      <c r="M15" s="18"/>
+      <c r="N15" s="18">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="O15" s="18">
+        <v>1.4870797280000001</v>
+      </c>
+      <c r="P15" s="18">
+        <v>0.41515672300000001</v>
+      </c>
+      <c r="Q15" s="18">
+        <v>3.1272250000000001E-2</v>
+      </c>
+      <c r="R15" s="18">
+        <v>2.6969479999999998E-3</v>
+      </c>
+      <c r="S15" s="18">
+        <v>1.6418242E-2</v>
+      </c>
+      <c r="T15" s="18">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="U15" s="18">
+        <v>6.0170000000000003</v>
+      </c>
+      <c r="V15" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W15" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X15" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y15" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z15" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA15" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB15" s="17">
+        <v>3.8657999999999998E-2</v>
+      </c>
+      <c r="AC15" s="17">
+        <v>0.28202989299999998</v>
+      </c>
+      <c r="AD15" s="17"/>
+      <c r="AE15" s="17"/>
+    </row>
+    <row r="16" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="11">
+        <v>11.83688910887013</v>
+      </c>
+      <c r="C16" s="12">
+        <v>2.872952807615337</v>
+      </c>
+      <c r="D16" s="11">
+        <v>19.852689651270651</v>
+      </c>
+      <c r="E16" s="12">
+        <v>18.438684278277609</v>
+      </c>
+      <c r="F16" s="11">
+        <v>2.586129998988012</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0.18</v>
+      </c>
+      <c r="I16" s="18">
+        <v>2.83</v>
+      </c>
+      <c r="J16" s="18">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="O16" s="18">
+        <v>1.069367508</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.18424942899999999</v>
+      </c>
+      <c r="Q16" s="18">
+        <v>2.652065E-2</v>
+      </c>
+      <c r="R16" s="18">
+        <v>0</v>
+      </c>
+      <c r="S16" s="18">
+        <v>1.5674206999999999E-2</v>
+      </c>
+      <c r="T16" s="18">
+        <v>6.2510000000000003</v>
+      </c>
+      <c r="U16" s="18">
+        <v>5.2640000000000002</v>
+      </c>
+      <c r="V16" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W16" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X16" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y16" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA16" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>3.7945E-2</v>
+      </c>
+      <c r="AC16" s="17">
+        <v>0.288119607</v>
+      </c>
+      <c r="AD16" s="17"/>
+      <c r="AE16" s="17"/>
+    </row>
+    <row r="17" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="11">
+        <v>13.630656462143801</v>
+      </c>
+      <c r="C17" s="12">
+        <v>3.6871746201584572</v>
+      </c>
+      <c r="D17" s="11">
+        <v>26.027669153478939</v>
+      </c>
+      <c r="E17" s="12">
+        <v>23.711743378380341</v>
+      </c>
+      <c r="F17" s="11">
+        <v>4.6690332585941317</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="I17" s="18">
+        <v>7.9909999999999997</v>
+      </c>
+      <c r="J17" s="18">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+      <c r="M17" s="18"/>
+      <c r="N17" s="18">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="O17" s="18">
+        <v>7.0441347099999998</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.31251037799999998</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>5.1692219999999997E-2</v>
+      </c>
+      <c r="R17" s="18">
+        <v>1.1339925000000001E-2</v>
+      </c>
+      <c r="S17" s="18">
+        <v>0</v>
+      </c>
+      <c r="T17" s="18">
+        <v>14.086</v>
+      </c>
+      <c r="U17" s="18">
+        <v>8.3010000000000002</v>
+      </c>
+      <c r="V17" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W17" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X17" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y17" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z17" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA17" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB17" s="17">
+        <v>4.7031000000000003E-2</v>
+      </c>
+      <c r="AC17" s="17">
+        <v>0.42247392900000003</v>
+      </c>
+      <c r="AD17" s="17"/>
+      <c r="AE17" s="17"/>
+    </row>
+    <row r="18" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="11">
+        <v>13.99990614878755</v>
+      </c>
+      <c r="C18" s="12">
+        <v>3.7830619536935601</v>
+      </c>
+      <c r="D18" s="11">
+        <v>25.092148890179701</v>
+      </c>
+      <c r="E18" s="12">
+        <v>22.652908378845389</v>
+      </c>
+      <c r="F18" s="11">
+        <v>4.8766062050264098</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="H18" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="I18" s="18">
+        <v>8.2759999999999998</v>
+      </c>
+      <c r="J18" s="18">
+        <v>1.6950000000000001</v>
+      </c>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18">
+        <v>1.6950000000000001</v>
+      </c>
+      <c r="O18" s="18">
+        <v>6.6847254490000001</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.27229536399999998</v>
+      </c>
+      <c r="Q18" s="18">
+        <v>4.4478275999999997E-2</v>
+      </c>
+      <c r="R18" s="18">
+        <v>3.4668667E-2</v>
+      </c>
+      <c r="S18" s="18">
+        <v>0</v>
+      </c>
+      <c r="T18" s="18">
+        <v>15.111000000000001</v>
+      </c>
+      <c r="U18" s="18">
+        <v>8.3870000000000005</v>
+      </c>
+      <c r="V18" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W18" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X18" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y18" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z18" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA18" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB18" s="17">
+        <v>4.5606000000000001E-2</v>
+      </c>
+      <c r="AC18" s="17">
+        <v>0.42133210700000001</v>
+      </c>
+      <c r="AD18" s="17"/>
+      <c r="AE18" s="17"/>
+    </row>
+    <row r="19" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="11">
+        <v>12.25440375923136</v>
+      </c>
+      <c r="C19" s="12">
+        <v>3.2421491924426808</v>
+      </c>
+      <c r="D19" s="11">
+        <v>22.478905114201829</v>
+      </c>
+      <c r="E19" s="12">
+        <v>20.389859308677689</v>
+      </c>
+      <c r="F19" s="11">
+        <v>4.0609425869293299</v>
+      </c>
+      <c r="G19" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H19" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="I19" s="18">
+        <v>8.9320000000000004</v>
+      </c>
+      <c r="J19" s="18">
+        <v>1.8660000000000001</v>
+      </c>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+      <c r="M19" s="18"/>
+      <c r="N19" s="18">
+        <v>1.8660000000000001</v>
+      </c>
+      <c r="O19" s="18">
+        <v>8.2124218889999998</v>
+      </c>
+      <c r="P19" s="18">
+        <v>0.61718923199999998</v>
+      </c>
+      <c r="Q19" s="18">
+        <v>6.4337543999999997E-2</v>
+      </c>
+      <c r="R19" s="18">
+        <v>2.9481279999999999E-2</v>
+      </c>
+      <c r="S19" s="18">
+        <v>0</v>
+      </c>
+      <c r="T19" s="18">
+        <v>16.956</v>
+      </c>
+      <c r="U19" s="18">
+        <v>9.34</v>
+      </c>
+      <c r="V19" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W19" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X19" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y19" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z19" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA19" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB19" s="17">
+        <v>5.2019000000000003E-2</v>
+      </c>
+      <c r="AC19" s="17">
+        <v>0.39963749999999998</v>
+      </c>
+      <c r="AD19" s="17"/>
+      <c r="AE19" s="17"/>
+    </row>
+    <row r="20" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="11">
+        <v>13.731150237672081</v>
+      </c>
+      <c r="C20" s="12">
+        <v>3.709337859762214</v>
+      </c>
+      <c r="D20" s="11">
+        <v>24.331381360800719</v>
+      </c>
+      <c r="E20" s="12">
+        <v>21.3375764331205</v>
+      </c>
+      <c r="F20" s="11">
+        <v>5.4347906080962067</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="H20" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="I20" s="18">
+        <v>12.936999999999999</v>
+      </c>
+      <c r="J20" s="18">
+        <v>2.7120000000000002</v>
+      </c>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+      <c r="M20" s="18"/>
+      <c r="N20" s="18">
+        <v>2.7120000000000002</v>
+      </c>
+      <c r="O20" s="18">
+        <v>11.927306959999999</v>
+      </c>
+      <c r="P20" s="18">
+        <v>0.47269426599999997</v>
+      </c>
+      <c r="Q20" s="18">
+        <v>8.9757966999999994E-2</v>
+      </c>
+      <c r="R20" s="18">
+        <v>3.5944587E-2</v>
+      </c>
+      <c r="S20" s="18">
+        <v>0</v>
+      </c>
+      <c r="T20" s="18">
+        <v>20.902000000000001</v>
+      </c>
+      <c r="U20" s="18">
+        <v>12.682</v>
+      </c>
+      <c r="V20" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W20" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X20" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y20" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z20" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA20" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB20" s="17">
+        <v>7.3219000000000006E-2</v>
+      </c>
+      <c r="AC20" s="17">
+        <v>0.48415467400000001</v>
+      </c>
+      <c r="AD20" s="17"/>
+      <c r="AE20" s="17"/>
+    </row>
+    <row r="21" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="11">
+        <v>14.71336679770886</v>
+      </c>
+      <c r="C21" s="12">
+        <v>3.501202473720594</v>
+      </c>
+      <c r="D21" s="11">
+        <v>26.777653603435621</v>
+      </c>
+      <c r="E21" s="12">
+        <v>24.194195484861549</v>
+      </c>
+      <c r="F21" s="11">
+        <v>4.6297077350518014</v>
+      </c>
+      <c r="G21" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="H21" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="I21" s="18">
+        <v>13.23</v>
+      </c>
+      <c r="J21" s="18">
+        <v>2.786</v>
+      </c>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18">
+        <v>2.786</v>
+      </c>
+      <c r="O21" s="18">
+        <v>12.12470377</v>
+      </c>
+      <c r="P21" s="18">
+        <v>0.63692599999999999</v>
+      </c>
+      <c r="Q21" s="18">
+        <v>0.104193063</v>
+      </c>
+      <c r="R21" s="18">
+        <v>3.3770889999999998E-2</v>
+      </c>
+      <c r="S21" s="18">
+        <v>0</v>
+      </c>
+      <c r="T21" s="18">
+        <v>21.082999999999998</v>
+      </c>
+      <c r="U21" s="18">
+        <v>12.353999999999999</v>
+      </c>
+      <c r="V21" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W21" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X21" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y21" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z21" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA21" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB21" s="17">
+        <v>7.0545999999999998E-2</v>
+      </c>
+      <c r="AC21" s="17">
+        <v>0.48992198300000001</v>
+      </c>
+      <c r="AD21" s="17"/>
+      <c r="AE21" s="17"/>
+    </row>
+    <row r="22" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="11">
+        <v>14.969682612902981</v>
+      </c>
+      <c r="C22" s="12">
+        <v>4.055934184196099</v>
+      </c>
+      <c r="D22" s="11">
+        <v>29.242721790770421</v>
+      </c>
+      <c r="E22" s="12">
+        <v>26.33247524146757</v>
+      </c>
+      <c r="F22" s="11">
+        <v>5.9115748203548577</v>
+      </c>
+      <c r="G22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="I22" s="18">
+        <v>13.096</v>
+      </c>
+      <c r="J22" s="18">
+        <v>2.742</v>
+      </c>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+      <c r="M22" s="18"/>
+      <c r="N22" s="18">
+        <v>2.742</v>
+      </c>
+      <c r="O22" s="18">
+        <v>11.84780602</v>
+      </c>
+      <c r="P22" s="18">
+        <v>0.47734259699999998</v>
+      </c>
+      <c r="Q22" s="18">
+        <v>9.1823417000000004E-2</v>
+      </c>
+      <c r="R22" s="18">
+        <v>0</v>
+      </c>
+      <c r="S22" s="18">
+        <v>0</v>
+      </c>
+      <c r="T22" s="18">
+        <v>21.097999999999999</v>
+      </c>
+      <c r="U22" s="18">
+        <v>12.977</v>
+      </c>
+      <c r="V22" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W22" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="X22" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="Y22" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z22" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA22" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="AB22" s="17">
+        <v>8.8717000000000004E-2</v>
+      </c>
+      <c r="AC22" s="17">
+        <v>0.50886425499999999</v>
+      </c>
+      <c r="AD22" s="17"/>
+      <c r="AE22" s="17"/>
+    </row>
+    <row r="23" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="11">
+        <v>16.431822737462831</v>
+      </c>
+      <c r="C23" s="12">
+        <v>5.0026057234162673</v>
+      </c>
+      <c r="D23" s="11">
+        <v>25.761668645821992</v>
+      </c>
+      <c r="E23" s="12">
+        <v>23.888971054252782</v>
+      </c>
+      <c r="F23" s="11">
+        <v>5.4206082079480256</v>
+      </c>
+      <c r="G23" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H23" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I23" s="18">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="J23" s="18"/>
+      <c r="K23" s="18">
+        <v>0.747</v>
+      </c>
+      <c r="L23" s="18"/>
+      <c r="M23" s="18"/>
+      <c r="N23" s="18">
+        <v>1.4930000000000001</v>
+      </c>
+      <c r="O23" s="18">
+        <v>0</v>
+      </c>
+      <c r="P23" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="18">
+        <v>8.7561730000000008E-3</v>
+      </c>
+      <c r="R23" s="18">
+        <v>0</v>
+      </c>
+      <c r="S23" s="18">
+        <v>0</v>
+      </c>
+      <c r="T23" s="18">
+        <v>2.7690000000000001</v>
+      </c>
+      <c r="U23" s="18">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="V23" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W23" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="X23" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="Y23" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z23" s="17">
+        <v>5</v>
+      </c>
+      <c r="AA23" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB23" s="17">
+        <v>7.1259000000000003E-2</v>
+      </c>
+      <c r="AC23" s="17">
+        <v>0.49783414300000001</v>
+      </c>
+      <c r="AD23" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE23" s="17"/>
+    </row>
+    <row r="24" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="11">
+        <v>20.225924725133741</v>
+      </c>
+      <c r="C24" s="12">
+        <v>6.0050979879260398</v>
+      </c>
+      <c r="D24" s="11">
+        <v>28.788274574161349</v>
+      </c>
+      <c r="E24" s="12">
+        <v>26.592628327160948</v>
+      </c>
+      <c r="F24" s="11">
+        <v>6.6341353665586764</v>
+      </c>
+      <c r="G24" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="H24" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I24" s="18">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="J24" s="18"/>
+      <c r="K24" s="18">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="L24" s="18"/>
+      <c r="M24" s="18"/>
+      <c r="N24" s="18">
+        <v>1.423</v>
+      </c>
+      <c r="O24" s="18">
+        <v>0</v>
+      </c>
+      <c r="P24" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="18">
+        <v>5.5182690000000001E-3</v>
+      </c>
+      <c r="R24" s="18">
+        <v>0</v>
+      </c>
+      <c r="S24" s="18">
+        <v>0</v>
+      </c>
+      <c r="T24" s="18">
+        <v>2.7170000000000001</v>
+      </c>
+      <c r="U24" s="18">
+        <v>2.3530000000000002</v>
+      </c>
+      <c r="V24" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W24" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="X24" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="Y24" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z24" s="17">
+        <v>5</v>
+      </c>
+      <c r="AA24" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB24" s="17">
+        <v>5.8789000000000001E-2</v>
+      </c>
+      <c r="AC24" s="17">
+        <v>0.58385135700000002</v>
+      </c>
+      <c r="AD24" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE24" s="17"/>
+    </row>
+    <row r="25" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="11">
+        <v>20.313130931321059</v>
+      </c>
+      <c r="C25" s="12">
+        <v>5.7257535596036906</v>
+      </c>
+      <c r="D25" s="11">
+        <v>29.805274443048681</v>
+      </c>
+      <c r="E25" s="12">
+        <v>27.630459578530338</v>
+      </c>
+      <c r="F25" s="11">
+        <v>6.0134781673316153</v>
+      </c>
+      <c r="G25" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="H25" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I25" s="18">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="J25" s="18"/>
+      <c r="K25" s="18">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="L25" s="18"/>
+      <c r="M25" s="18"/>
+      <c r="N25" s="18">
+        <v>1.3819999999999999</v>
+      </c>
+      <c r="O25" s="18">
+        <v>0</v>
+      </c>
+      <c r="P25" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="18">
+        <v>1.9902549999999998E-3</v>
+      </c>
+      <c r="R25" s="18">
+        <v>0</v>
+      </c>
+      <c r="S25" s="18">
+        <v>0</v>
+      </c>
+      <c r="T25" s="18">
+        <v>2.5739999999999998</v>
+      </c>
+      <c r="U25" s="18">
+        <v>2.25</v>
+      </c>
+      <c r="V25" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W25" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="X25" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="Y25" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z25" s="17">
+        <v>5</v>
+      </c>
+      <c r="AA25" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB25" s="17">
+        <v>6.4132999999999996E-2</v>
+      </c>
+      <c r="AC25" s="17">
+        <v>0.59412774999999995</v>
+      </c>
+      <c r="AD25" s="17" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE25" s="17"/>
+    </row>
+    <row r="26" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="11">
+        <v>17.79580945554655</v>
+      </c>
+      <c r="C26" s="12">
+        <v>4.9645003397723828</v>
+      </c>
+      <c r="D26" s="11">
+        <v>29.752777306453648</v>
+      </c>
+      <c r="E26" s="12">
+        <v>27.843615623634062</v>
+      </c>
+      <c r="F26" s="11">
+        <v>4.8458917252374976</v>
+      </c>
+      <c r="G26" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="H26" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I26" s="18">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="J26" s="18"/>
+      <c r="K26" s="18">
+        <v>4.92</v>
+      </c>
+      <c r="L26" s="18"/>
+      <c r="M26" s="18"/>
+      <c r="N26" s="18">
+        <v>9.8390000000000004</v>
+      </c>
+      <c r="O26" s="18">
+        <v>0</v>
+      </c>
+      <c r="P26" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="18">
+        <v>3.9436786000000001E-2</v>
+      </c>
+      <c r="R26" s="18">
+        <v>0</v>
+      </c>
+      <c r="S26" s="18">
+        <v>1.3630471999999999E-2</v>
+      </c>
+      <c r="T26" s="18">
+        <v>3.032</v>
+      </c>
+      <c r="U26" s="18">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="V26" s="19">
+        <v>1.21</v>
+      </c>
+      <c r="W26" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="X26" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="Y26" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z26" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA26" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB26" s="17">
+        <v>5.5581999999999999E-2</v>
+      </c>
+      <c r="AC26" s="17">
+        <v>0.510013571</v>
+      </c>
+      <c r="AD26" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="AE26" s="17"/>
+    </row>
+    <row r="27" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="11">
+        <v>11.203152265193641</v>
+      </c>
+      <c r="C27" s="12">
+        <v>3.10958544873849</v>
+      </c>
+      <c r="D27" s="11">
+        <v>16.06992224208037</v>
+      </c>
+      <c r="E27" s="12">
+        <v>14.598228135166041</v>
+      </c>
+      <c r="F27" s="11">
+        <v>2.8233950705989139</v>
+      </c>
+      <c r="G27" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="H27" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I27" s="18">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18">
+        <v>3.9620000000000002</v>
+      </c>
+      <c r="L27" s="18"/>
+      <c r="M27" s="18"/>
+      <c r="N27" s="18">
+        <v>7.9240000000000004</v>
+      </c>
+      <c r="O27" s="18">
+        <v>0</v>
+      </c>
+      <c r="P27" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="18">
+        <v>3.0460814999999999E-2</v>
+      </c>
+      <c r="R27" s="18">
+        <v>0</v>
+      </c>
+      <c r="S27" s="18">
+        <v>9.5061450000000006E-3</v>
+      </c>
+      <c r="T27" s="18">
+        <v>1.9590000000000001</v>
+      </c>
+      <c r="U27" s="18">
+        <v>1.623</v>
+      </c>
+      <c r="V27" s="19">
+        <v>1.21</v>
+      </c>
+      <c r="W27" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="X27" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="Y27" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z27" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA27" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB27" s="17">
+        <v>5.4869000000000001E-2</v>
+      </c>
+      <c r="AC27" s="17">
+        <v>0.29420932100000002</v>
+      </c>
+      <c r="AD27" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="AE27" s="17"/>
+    </row>
+    <row r="28" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="11">
+        <v>13.944051036203639</v>
+      </c>
+      <c r="C28" s="12">
+        <v>3.6883708173681802</v>
+      </c>
+      <c r="D28" s="11">
+        <v>19.233553532682901</v>
+      </c>
+      <c r="E28" s="12">
+        <v>17.380680153739881</v>
+      </c>
+      <c r="F28" s="11">
+        <v>3.2031348985010988</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I28" s="18">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="J28" s="18"/>
+      <c r="K28" s="18">
+        <v>4.6159999999999997</v>
+      </c>
+      <c r="L28" s="18"/>
+      <c r="M28" s="18"/>
+      <c r="N28" s="18">
+        <v>9.2319999999999993</v>
+      </c>
+      <c r="O28" s="18">
+        <v>0</v>
+      </c>
+      <c r="P28" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="18">
+        <v>2.5119712999999998E-2</v>
+      </c>
+      <c r="R28" s="18">
+        <v>0</v>
+      </c>
+      <c r="S28" s="18">
+        <v>0</v>
+      </c>
+      <c r="T28" s="18">
+        <v>2.569</v>
+      </c>
+      <c r="U28" s="18">
+        <v>1.2909999999999999</v>
+      </c>
+      <c r="V28" s="19">
+        <v>1.21</v>
+      </c>
+      <c r="W28" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="X28" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="Y28" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z28" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA28" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB28" s="17">
+        <v>5.1663000000000001E-2</v>
+      </c>
+      <c r="AC28" s="17">
+        <v>0.358912536</v>
+      </c>
+      <c r="AD28" s="17" t="s">
+        <v>255</v>
+      </c>
+      <c r="AE28" s="17"/>
+    </row>
+    <row r="29" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="11">
+        <v>10.989985341219221</v>
+      </c>
+      <c r="C29" s="12">
+        <v>2.2106874227740461</v>
+      </c>
+      <c r="D29" s="11">
+        <v>13.06327284794153</v>
+      </c>
+      <c r="E29" s="12">
+        <v>11.791325157574761</v>
+      </c>
+      <c r="F29" s="11">
+        <v>2.1433134481696849</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I29" s="18">
+        <v>1.381</v>
+      </c>
+      <c r="J29" s="18"/>
+      <c r="K29" s="18">
+        <v>0.158</v>
+      </c>
+      <c r="L29" s="18"/>
+      <c r="M29" s="18"/>
+      <c r="N29" s="18">
+        <v>0.317</v>
+      </c>
+      <c r="O29" s="18">
+        <v>1.8073279000000001E-2</v>
+      </c>
+      <c r="P29" s="18">
+        <v>7.8381013999999999E-2</v>
+      </c>
+      <c r="Q29" s="18">
+        <v>0.86713414300000002</v>
+      </c>
+      <c r="R29" s="18">
+        <v>5.4564440000000004E-3</v>
+      </c>
+      <c r="S29" s="18">
+        <v>4.6616212999999997E-2</v>
+      </c>
+      <c r="T29" s="18">
+        <v>4.3209999999999997</v>
+      </c>
+      <c r="U29" s="18">
+        <v>3.883</v>
+      </c>
+      <c r="V29" s="19">
+        <v>6.87</v>
+      </c>
+      <c r="W29" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="X29" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Y29" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z29" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA29" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB29" s="17">
+        <v>2.6366000000000001E-2</v>
+      </c>
+      <c r="AC29" s="17">
+        <v>0.20552785700000001</v>
+      </c>
+      <c r="AD29" s="17"/>
+      <c r="AE29" s="17"/>
+    </row>
+    <row r="30" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="11">
+        <v>17.248266534448302</v>
+      </c>
+      <c r="C30" s="12">
+        <v>3.7514499623161099</v>
+      </c>
+      <c r="D30" s="11">
+        <v>23.660050499583871</v>
+      </c>
+      <c r="E30" s="12">
+        <v>21.93278932501935</v>
+      </c>
+      <c r="F30" s="11">
+        <v>3.5369743666809978</v>
+      </c>
+      <c r="G30" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="H30" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I30" s="18">
+        <v>1.2589999999999999</v>
+      </c>
+      <c r="J30" s="18"/>
+      <c r="K30" s="18">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="L30" s="18"/>
+      <c r="M30" s="18"/>
+      <c r="N30" s="18">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="O30" s="18">
+        <v>0</v>
+      </c>
+      <c r="P30" s="18">
+        <v>3.4333113999999998E-2</v>
+      </c>
+      <c r="Q30" s="18">
+        <v>0.69158415699999998</v>
+      </c>
+      <c r="R30" s="18">
+        <v>0</v>
+      </c>
+      <c r="S30" s="18">
+        <v>4.5041784000000001E-2</v>
+      </c>
+      <c r="T30" s="18">
+        <v>3.93</v>
+      </c>
+      <c r="U30" s="18">
+        <v>3.3959999999999999</v>
+      </c>
+      <c r="V30" s="19">
+        <v>6.87</v>
+      </c>
+      <c r="W30" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="X30" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Y30" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z30" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA30" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB30" s="17">
+        <v>2.2268E-2</v>
+      </c>
+      <c r="AC30" s="17">
+        <v>0.35282282100000001</v>
+      </c>
+      <c r="AD30" s="17"/>
+      <c r="AE30" s="17"/>
+    </row>
+    <row r="31" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="11">
+        <v>15.952828145951839</v>
+      </c>
+      <c r="C31" s="12">
+        <v>3.6563421813446868</v>
+      </c>
+      <c r="D31" s="11">
+        <v>23.69858741990603</v>
+      </c>
+      <c r="E31" s="12">
+        <v>22.052331279615661</v>
+      </c>
+      <c r="F31" s="11">
+        <v>3.616512483090192</v>
+      </c>
+      <c r="G31" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H31" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I31" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="J31" s="18"/>
+      <c r="K31" s="18">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="L31" s="18"/>
+      <c r="M31" s="18"/>
+      <c r="N31" s="18">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="O31" s="18">
+        <v>0</v>
+      </c>
+      <c r="P31" s="18">
+        <v>7.6426068999999999E-2</v>
+      </c>
+      <c r="Q31" s="18">
+        <v>0.84262339500000005</v>
+      </c>
+      <c r="R31" s="18">
+        <v>5.663179E-3</v>
+      </c>
+      <c r="S31" s="18">
+        <v>4.1991897E-2</v>
+      </c>
+      <c r="T31" s="18">
+        <v>4.077</v>
+      </c>
+      <c r="U31" s="18">
+        <v>3.3340000000000001</v>
+      </c>
+      <c r="V31" s="19">
+        <v>6.87</v>
+      </c>
+      <c r="W31" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="X31" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Y31" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z31" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA31" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB31" s="17">
+        <v>1.7815000000000001E-2</v>
+      </c>
+      <c r="AC31" s="17">
+        <v>0.36195739300000002</v>
+      </c>
+      <c r="AD31" s="17"/>
+      <c r="AE31" s="17"/>
+    </row>
+    <row r="32" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="11">
+        <v>17.777593841658859</v>
+      </c>
+      <c r="C32" s="12">
+        <v>5.8352277076181887</v>
+      </c>
+      <c r="D32" s="11">
+        <v>24.708218560609222</v>
+      </c>
+      <c r="E32" s="12">
+        <v>22.704998483168261</v>
+      </c>
+      <c r="F32" s="11">
+        <v>7.3992106470754324</v>
+      </c>
+      <c r="G32" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H32" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I32" s="18">
+        <v>1.4850000000000001</v>
+      </c>
+      <c r="J32" s="18"/>
+      <c r="K32" s="18"/>
+      <c r="L32" s="18">
+        <v>2.8620000000000001</v>
+      </c>
+      <c r="M32" s="18"/>
+      <c r="N32" s="18">
+        <v>2.8620000000000001</v>
+      </c>
+      <c r="O32" s="18">
+        <v>0</v>
+      </c>
+      <c r="P32" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="18">
+        <v>6.3162172000000003E-2</v>
+      </c>
+      <c r="R32" s="18">
+        <v>0</v>
+      </c>
+      <c r="S32" s="18">
+        <v>0</v>
+      </c>
+      <c r="T32" s="18">
+        <v>5.7110000000000003</v>
+      </c>
+      <c r="U32" s="18">
+        <v>5.6040000000000001</v>
+      </c>
+      <c r="V32" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W32" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="X32" s="17">
+        <v>12.35</v>
+      </c>
+      <c r="Y32" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z32" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA32" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB32" s="17">
+        <v>1.9595999999999999E-2</v>
+      </c>
+      <c r="AC32" s="17">
+        <v>0.425138179</v>
+      </c>
+      <c r="AD32" s="17"/>
+      <c r="AE32" s="17"/>
+    </row>
+    <row r="33" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="11">
+        <v>20.884398045016169</v>
+      </c>
+      <c r="C33" s="12">
+        <v>6.4707515227445249</v>
+      </c>
+      <c r="D33" s="11">
+        <v>30.395958128395421</v>
+      </c>
+      <c r="E33" s="12">
+        <v>28.220530245934022</v>
+      </c>
+      <c r="F33" s="11">
+        <v>8.5514293292577772</v>
+      </c>
+      <c r="G33" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="H33" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I33" s="18">
+        <v>1.6</v>
+      </c>
+      <c r="J33" s="18"/>
+      <c r="K33" s="18"/>
+      <c r="L33" s="18">
+        <v>3.0840000000000001</v>
+      </c>
+      <c r="M33" s="18"/>
+      <c r="N33" s="18">
+        <v>3.0840000000000001</v>
+      </c>
+      <c r="O33" s="18">
+        <v>0</v>
+      </c>
+      <c r="P33" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="18">
+        <v>7.4209667000000007E-2</v>
+      </c>
+      <c r="R33" s="18">
+        <v>0</v>
+      </c>
+      <c r="S33" s="18">
+        <v>0</v>
+      </c>
+      <c r="T33" s="18">
+        <v>6.0389999999999997</v>
+      </c>
+      <c r="U33" s="18">
+        <v>5.8689999999999998</v>
+      </c>
+      <c r="V33" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W33" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="X33" s="17">
+        <v>12.35</v>
+      </c>
+      <c r="Y33" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z33" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA33" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB33" s="17">
+        <v>2.0309000000000001E-2</v>
+      </c>
+      <c r="AC33" s="17">
+        <v>0.52028996400000005</v>
+      </c>
+      <c r="AD33" s="17"/>
+      <c r="AE33" s="17"/>
+    </row>
+    <row r="34" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="11">
+        <v>18.890203683745039</v>
+      </c>
+      <c r="C34" s="12">
+        <v>5.8525559106846634</v>
+      </c>
+      <c r="D34" s="11">
+        <v>26.737275531321369</v>
+      </c>
+      <c r="E34" s="12">
+        <v>24.61170757727465</v>
+      </c>
+      <c r="F34" s="11">
+        <v>8.0366685880295137</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="H34" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I34" s="18">
+        <v>1.4350000000000001</v>
+      </c>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+      <c r="L34" s="18">
+        <v>2.7629999999999999</v>
+      </c>
+      <c r="M34" s="18"/>
+      <c r="N34" s="18">
+        <v>2.7629999999999999</v>
+      </c>
+      <c r="O34" s="18">
+        <v>0</v>
+      </c>
+      <c r="P34" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="18">
+        <v>7.4921513999999995E-2</v>
+      </c>
+      <c r="R34" s="18">
+        <v>0</v>
+      </c>
+      <c r="S34" s="18">
+        <v>0</v>
+      </c>
+      <c r="T34" s="18">
+        <v>5.32</v>
+      </c>
+      <c r="U34" s="18">
+        <v>5.0789999999999997</v>
+      </c>
+      <c r="V34" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W34" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="X34" s="17">
+        <v>12.35</v>
+      </c>
+      <c r="Y34" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z34" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA34" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB34" s="17">
+        <v>1.8171E-2</v>
+      </c>
+      <c r="AC34" s="17">
+        <v>0.452161286</v>
+      </c>
+      <c r="AD34" s="17"/>
+      <c r="AE34" s="17"/>
+    </row>
+    <row r="35" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="11">
+        <v>19.077701954263681</v>
+      </c>
+      <c r="C35" s="12">
+        <v>4.2169240194796247</v>
+      </c>
+      <c r="D35" s="11">
+        <v>26.701951055833131</v>
+      </c>
+      <c r="E35" s="12">
+        <v>24.908111456937021</v>
+      </c>
+      <c r="F35" s="11">
+        <v>3.736156336730533</v>
+      </c>
+      <c r="G35" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="H35" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I35" s="18">
+        <v>1.6779999999999999</v>
+      </c>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+      <c r="L35" s="18">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="M35" s="18"/>
+      <c r="N35" s="18">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="O35" s="18">
+        <v>0</v>
+      </c>
+      <c r="P35" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="18">
+        <v>0.27117874199999997</v>
+      </c>
+      <c r="R35" s="18">
+        <v>0</v>
+      </c>
+      <c r="S35" s="18">
+        <v>0</v>
+      </c>
+      <c r="T35" s="18">
+        <v>5.7240000000000002</v>
+      </c>
+      <c r="U35" s="18">
+        <v>5.9080000000000004</v>
+      </c>
+      <c r="V35" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W35" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="X35" s="17">
+        <v>1.24</v>
+      </c>
+      <c r="Y35" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z35" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA35" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB35" s="17">
+        <v>2.3337E-2</v>
+      </c>
+      <c r="AC35" s="17">
+        <v>0.41790664300000002</v>
+      </c>
+      <c r="AD35" s="17"/>
+      <c r="AE35" s="17"/>
+    </row>
+    <row r="36" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="11">
+        <v>18.058748256177928</v>
+      </c>
+      <c r="C36" s="12">
+        <v>3.926920303068532</v>
+      </c>
+      <c r="D36" s="11">
+        <v>25.395769344687949</v>
+      </c>
+      <c r="E36" s="12">
+        <v>23.61807028229504</v>
+      </c>
+      <c r="F36" s="11">
+        <v>3.781250662444779</v>
+      </c>
+      <c r="G36" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="H36" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I36" s="18">
+        <v>1.6930000000000001</v>
+      </c>
+      <c r="J36" s="18"/>
+      <c r="K36" s="18"/>
+      <c r="L36" s="18">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="M36" s="18"/>
+      <c r="N36" s="18">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="O36" s="18">
+        <v>0</v>
+      </c>
+      <c r="P36" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="18">
+        <v>0.30716928599999999</v>
+      </c>
+      <c r="R36" s="18">
+        <v>0</v>
+      </c>
+      <c r="S36" s="18">
+        <v>0</v>
+      </c>
+      <c r="T36" s="18">
+        <v>5.9720000000000004</v>
+      </c>
+      <c r="U36" s="18">
+        <v>5.29</v>
+      </c>
+      <c r="V36" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W36" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="X36" s="17">
+        <v>1.24</v>
+      </c>
+      <c r="Y36" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z36" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA36" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB36" s="17">
+        <v>2.4941000000000001E-2</v>
+      </c>
+      <c r="AC36" s="17">
+        <v>0.37870410700000001</v>
+      </c>
+      <c r="AD36" s="17"/>
+      <c r="AE36" s="17"/>
+    </row>
+    <row r="37" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="11">
+        <v>18.10451954340164</v>
+      </c>
+      <c r="C37" s="12">
+        <v>3.8801333979303338</v>
+      </c>
+      <c r="D37" s="11">
+        <v>28.572772066587842</v>
+      </c>
+      <c r="E37" s="12">
+        <v>26.728869747233201</v>
+      </c>
+      <c r="F37" s="11">
+        <v>4.5269598183644622</v>
+      </c>
+      <c r="G37" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="H37" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I37" s="18">
+        <v>1.647</v>
+      </c>
+      <c r="J37" s="18"/>
+      <c r="K37" s="18"/>
+      <c r="L37" s="18">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="M37" s="18"/>
+      <c r="N37" s="18">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="O37" s="18">
+        <v>0</v>
+      </c>
+      <c r="P37" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="18">
+        <v>0.20397084300000001</v>
+      </c>
+      <c r="R37" s="18">
+        <v>0</v>
+      </c>
+      <c r="S37" s="18">
+        <v>0</v>
+      </c>
+      <c r="T37" s="18">
+        <v>6.1310000000000002</v>
+      </c>
+      <c r="U37" s="18">
+        <v>5.69</v>
+      </c>
+      <c r="V37" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W37" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="X37" s="17">
+        <v>1.24</v>
+      </c>
+      <c r="Y37" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z37" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA37" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB37" s="17">
+        <v>2.4406000000000001E-2</v>
+      </c>
+      <c r="AC37" s="17">
+        <v>0.39887628600000002</v>
+      </c>
+      <c r="AD37" s="17"/>
+      <c r="AE37" s="17"/>
+    </row>
+    <row r="38" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="11">
+        <v>11.942458667755201</v>
+      </c>
+      <c r="C38" s="12">
+        <v>3.2785210634010742</v>
+      </c>
+      <c r="D38" s="11">
+        <v>20.665863556430679</v>
+      </c>
+      <c r="E38" s="12">
+        <v>19.16786522084951</v>
+      </c>
+      <c r="F38" s="11">
+        <v>3.1451417516310789</v>
+      </c>
+      <c r="G38" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H38" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I38" s="18">
+        <v>1.4790000000000001</v>
+      </c>
+      <c r="J38" s="18"/>
+      <c r="K38" s="18"/>
+      <c r="L38" s="18"/>
+      <c r="M38" s="18">
+        <v>2.919</v>
+      </c>
+      <c r="N38" s="18">
+        <v>2.919</v>
+      </c>
+      <c r="O38" s="18">
+        <v>6.4434642E-2</v>
+      </c>
+      <c r="P38" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="18">
+        <v>0.16559933199999999</v>
+      </c>
+      <c r="R38" s="18">
+        <v>0</v>
+      </c>
+      <c r="S38" s="18">
+        <v>4.8736990000000004E-3</v>
+      </c>
+      <c r="T38" s="18">
+        <v>4.7869999999999999</v>
+      </c>
+      <c r="U38" s="18">
+        <v>4.5609999999999999</v>
+      </c>
+      <c r="V38" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W38" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="X38" s="17">
+        <v>9.81</v>
+      </c>
+      <c r="Y38" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z38" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA38" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB38" s="17">
+        <v>2.9215999999999999E-2</v>
+      </c>
+      <c r="AC38" s="17">
+        <v>0.32085182099999998</v>
+      </c>
+      <c r="AD38" s="17"/>
+      <c r="AE38" s="17"/>
+    </row>
+    <row r="39" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="11">
+        <v>15.27361175403189</v>
+      </c>
+      <c r="C39" s="12">
+        <v>4.2747420805227527</v>
+      </c>
+      <c r="D39" s="11">
+        <v>24.982330706603769</v>
+      </c>
+      <c r="E39" s="12">
+        <v>23.16353773573416</v>
+      </c>
+      <c r="F39" s="11">
+        <v>4.1224151411254093</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="H39" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I39" s="18">
+        <v>1.633</v>
+      </c>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+      <c r="L39" s="18"/>
+      <c r="M39" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="N39" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="O39" s="18">
+        <v>0</v>
+      </c>
+      <c r="P39" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="18">
+        <v>0.156217087</v>
+      </c>
+      <c r="R39" s="18">
+        <v>0</v>
+      </c>
+      <c r="S39" s="18">
+        <v>0</v>
+      </c>
+      <c r="T39" s="18">
+        <v>5.1379999999999999</v>
+      </c>
+      <c r="U39" s="18">
+        <v>4.9089999999999998</v>
+      </c>
+      <c r="V39" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W39" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="X39" s="17">
+        <v>9.81</v>
+      </c>
+      <c r="Y39" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z39" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA39" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB39" s="17">
+        <v>3.4738999999999999E-2</v>
+      </c>
+      <c r="AC39" s="17">
+        <v>0.41866785699999998</v>
+      </c>
+      <c r="AD39" s="17"/>
+      <c r="AE39" s="17"/>
+    </row>
+    <row r="40" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="11">
+        <v>12.167715689720319</v>
+      </c>
+      <c r="C40" s="12">
+        <v>3.5298212245888161</v>
+      </c>
+      <c r="D40" s="11">
+        <v>18.220083395992031</v>
+      </c>
+      <c r="E40" s="12">
+        <v>16.563008404594981</v>
+      </c>
+      <c r="F40" s="11">
+        <v>3.0217809323285381</v>
+      </c>
+      <c r="G40" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="H40" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I40" s="18">
+        <v>1.571</v>
+      </c>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+      <c r="L40" s="18"/>
+      <c r="M40" s="18">
+        <v>3.0830000000000002</v>
+      </c>
+      <c r="N40" s="18">
+        <v>3.0830000000000002</v>
+      </c>
+      <c r="O40" s="18">
+        <v>6.4504826000000001E-2</v>
+      </c>
+      <c r="P40" s="18">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="18">
+        <v>0.15037355499999999</v>
+      </c>
+      <c r="R40" s="18">
+        <v>0</v>
+      </c>
+      <c r="S40" s="18">
+        <v>5.596462E-3</v>
+      </c>
+      <c r="T40" s="18">
+        <v>4.9610000000000003</v>
+      </c>
+      <c r="U40" s="18">
+        <v>4.5490000000000004</v>
+      </c>
+      <c r="V40" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W40" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="X40" s="17">
+        <v>9.81</v>
+      </c>
+      <c r="Y40" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="Z40" s="17">
+        <v>3</v>
+      </c>
+      <c r="AA40" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB40" s="17">
+        <v>3.0641000000000002E-2</v>
+      </c>
+      <c r="AC40" s="17">
+        <v>0.33150882100000001</v>
+      </c>
+      <c r="AD40" s="17"/>
+      <c r="AE40" s="17"/>
+    </row>
+    <row r="41" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="11">
+        <v>20.609642596596</v>
+      </c>
+      <c r="C41" s="12">
+        <v>4.5580518639193093</v>
+      </c>
+      <c r="D41" s="11">
+        <v>26.02321417818068</v>
+      </c>
+      <c r="E41" s="12">
+        <v>23.643671272043171</v>
+      </c>
+      <c r="F41" s="11">
+        <v>4.0532192934484366</v>
+      </c>
+      <c r="G41" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="H41" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I41" s="18">
+        <v>1.4510000000000001</v>
+      </c>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+      <c r="L41" s="18"/>
+      <c r="M41" s="18">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="N41" s="18">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="O41" s="18">
+        <v>0.16597783599999999</v>
+      </c>
+      <c r="P41" s="18">
+        <v>6.6479359000000002E-2</v>
+      </c>
+      <c r="Q41" s="18">
+        <v>0.60819290000000004</v>
+      </c>
+      <c r="R41" s="18">
+        <v>0</v>
+      </c>
+      <c r="S41" s="18">
+        <v>2.5725250000000002E-2</v>
+      </c>
+      <c r="T41" s="18">
+        <v>4.18</v>
+      </c>
+      <c r="U41" s="18">
+        <v>4.0129999999999999</v>
+      </c>
+      <c r="V41" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W41" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="X41" s="17">
+        <v>0.98</v>
+      </c>
+      <c r="Y41" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z41" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA41" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB41" s="17">
+        <v>2.4761999999999999E-2</v>
+      </c>
+      <c r="AC41" s="17">
+        <v>0.43998185699999998</v>
+      </c>
+      <c r="AD41" s="17"/>
+      <c r="AE41" s="17"/>
+    </row>
+    <row r="42" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="11">
+        <v>19.598279279981458</v>
+      </c>
+      <c r="C42" s="12">
+        <v>4.1381634199067587</v>
+      </c>
+      <c r="D42" s="11">
+        <v>28.398739942899439</v>
+      </c>
+      <c r="E42" s="12">
+        <v>26.212379598794769</v>
+      </c>
+      <c r="F42" s="11">
+        <v>4.3291385422259614</v>
+      </c>
+      <c r="G42" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="H42" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I42" s="18">
+        <v>1.7090000000000001</v>
+      </c>
+      <c r="J42" s="18"/>
+      <c r="K42" s="18"/>
+      <c r="L42" s="18"/>
+      <c r="M42" s="18">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="N42" s="18">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="O42" s="18">
+        <v>6.0174350000000001E-2</v>
+      </c>
+      <c r="P42" s="18">
+        <v>7.8079274000000004E-2</v>
+      </c>
+      <c r="Q42" s="18">
+        <v>0.66867871400000001</v>
+      </c>
+      <c r="R42" s="18">
+        <v>0</v>
+      </c>
+      <c r="S42" s="18">
+        <v>3.5868012999999997E-2</v>
+      </c>
+      <c r="T42" s="18">
+        <v>4.9020000000000001</v>
+      </c>
+      <c r="U42" s="18">
+        <v>4.45</v>
+      </c>
+      <c r="V42" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W42" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="X42" s="17">
+        <v>0.98</v>
+      </c>
+      <c r="Y42" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z42" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA42" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB42" s="17">
+        <v>2.1912000000000001E-2</v>
+      </c>
+      <c r="AC42" s="17">
+        <v>0.448355214</v>
+      </c>
+      <c r="AD42" s="17"/>
+      <c r="AE42" s="17"/>
+    </row>
+    <row r="43" spans="1:31" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="11">
+        <v>18.13617499884791</v>
+      </c>
+      <c r="C43" s="12">
+        <v>3.7846264298834682</v>
+      </c>
+      <c r="D43" s="11">
+        <v>25.547541711959809</v>
+      </c>
+      <c r="E43" s="12">
+        <v>23.409840647541621</v>
+      </c>
+      <c r="F43" s="11">
+        <v>3.681876056647718</v>
+      </c>
+      <c r="G43" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="H43" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="I43" s="18">
+        <v>1.6220000000000001</v>
+      </c>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+      <c r="L43" s="18"/>
+      <c r="M43" s="18">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="N43" s="18">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="O43" s="18">
+        <v>0.18362290100000001</v>
+      </c>
+      <c r="P43" s="18">
+        <v>0.16825845</v>
+      </c>
+      <c r="Q43" s="18">
+        <v>0.92271634599999997</v>
+      </c>
+      <c r="R43" s="18">
+        <v>0</v>
+      </c>
+      <c r="S43" s="18">
+        <v>4.8272586999999999E-2</v>
+      </c>
+      <c r="T43" s="18">
+        <v>4.5620000000000003</v>
+      </c>
+      <c r="U43" s="18">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="V43" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="W43" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="X43" s="17">
+        <v>0.98</v>
+      </c>
+      <c r="Y43" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="Z43" s="17">
+        <v>30</v>
+      </c>
+      <c r="AA43" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="AB43" s="17">
+        <v>2.4761999999999999E-2</v>
+      </c>
+      <c r="AC43" s="17">
+        <v>0.42361575000000001</v>
+      </c>
+      <c r="AD43" s="17"/>
+      <c r="AE43" s="17"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47F2821A-4F98-B24B-A835-DEBDEDB1FD86}">
+  <dimension ref="A1:Y43"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:25" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>226</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="M1" s="15" t="s">
+        <v>234</v>
+      </c>
+      <c r="N1" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="O1" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="P1" s="14" t="s">
+        <v>237</v>
+      </c>
+      <c r="Q1" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="R1" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="S1" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="V1" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="X1" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="Y1" s="15" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A2" s="16" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="C2" s="18">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="D2" s="18">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18">
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="I2" s="18">
+        <v>0</v>
+      </c>
+      <c r="J2" s="18">
+        <v>0</v>
+      </c>
+      <c r="K2" s="18">
+        <v>7.2308500000000005E-4</v>
+      </c>
+      <c r="L2" s="18">
+        <v>0</v>
+      </c>
+      <c r="M2" s="18">
+        <v>4.0285879999999996E-3</v>
+      </c>
+      <c r="N2" s="18">
+        <v>2.4449999999999998</v>
+      </c>
+      <c r="O2" s="18">
+        <v>2.3620000000000001</v>
+      </c>
+      <c r="P2" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q2" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R2" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S2" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T2" s="17">
+        <v>30</v>
+      </c>
+      <c r="U2" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V2" s="17">
+        <v>2.1734E-2</v>
+      </c>
+      <c r="W2" s="17">
+        <v>0.27251471399999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A3" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="C3" s="18">
+        <v>0.70399999999999996</v>
+      </c>
+      <c r="D3" s="18">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18">
+        <v>8.6999999999999994E-2</v>
+      </c>
+      <c r="I3" s="18">
+        <v>0</v>
+      </c>
+      <c r="J3" s="18">
+        <v>0</v>
+      </c>
+      <c r="K3" s="18">
+        <v>1.6583900000000001E-4</v>
+      </c>
+      <c r="L3" s="18">
+        <v>0</v>
+      </c>
+      <c r="M3" s="18">
+        <v>6.6796169999999997E-3</v>
+      </c>
+      <c r="N3" s="18">
+        <v>2.105</v>
+      </c>
+      <c r="O3" s="18">
+        <v>2.2759999999999998</v>
+      </c>
+      <c r="P3" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q3" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R3" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S3" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T3" s="17">
+        <v>30</v>
+      </c>
+      <c r="U3" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V3" s="17">
+        <v>2.4941000000000001E-2</v>
+      </c>
+      <c r="W3" s="17">
+        <v>0.25082010700000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="17">
+        <v>0.05</v>
+      </c>
+      <c r="C4" s="18">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="D4" s="18">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18">
+        <v>0.14000000000000001</v>
+      </c>
+      <c r="I4" s="18">
+        <v>0</v>
+      </c>
+      <c r="J4" s="18">
+        <v>0</v>
+      </c>
+      <c r="K4" s="18">
+        <v>3.81541E-4</v>
+      </c>
+      <c r="L4" s="18">
+        <v>0</v>
+      </c>
+      <c r="M4" s="18">
+        <v>9.7823159999999992E-3</v>
+      </c>
+      <c r="N4" s="18">
+        <v>2.383</v>
+      </c>
+      <c r="O4" s="18">
+        <v>1.6240000000000001</v>
+      </c>
+      <c r="P4" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q4" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R4" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S4" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T4" s="17">
+        <v>30</v>
+      </c>
+      <c r="U4" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V4" s="17">
+        <v>2.5831E-2</v>
+      </c>
+      <c r="W4" s="17">
+        <v>0.26109650000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C5" s="18">
+        <v>1.18</v>
+      </c>
+      <c r="D5" s="18">
+        <v>2.2029999999999998</v>
+      </c>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18">
+        <v>2.2029999999999998</v>
+      </c>
+      <c r="I5" s="18">
+        <v>0</v>
+      </c>
+      <c r="J5" s="18">
+        <v>0</v>
+      </c>
+      <c r="K5" s="18">
+        <v>1.2795499999999999E-4</v>
+      </c>
+      <c r="L5" s="18">
+        <v>0</v>
+      </c>
+      <c r="M5" s="18">
+        <v>0</v>
+      </c>
+      <c r="N5" s="18">
+        <v>1.93</v>
+      </c>
+      <c r="O5" s="18">
+        <v>2.44</v>
+      </c>
+      <c r="P5" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q5" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R5" s="17">
+        <v>5</v>
+      </c>
+      <c r="S5" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T5" s="17">
+        <v>3</v>
+      </c>
+      <c r="U5" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V5" s="17">
+        <v>5.3443999999999998E-2</v>
+      </c>
+      <c r="W5" s="17">
+        <v>0.35967375000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A6" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C6" s="18">
+        <v>1.127</v>
+      </c>
+      <c r="D6" s="18">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18">
+        <v>2.0979999999999999</v>
+      </c>
+      <c r="I6" s="18">
+        <v>1.6766474999999999E-2</v>
+      </c>
+      <c r="J6" s="18">
+        <v>0</v>
+      </c>
+      <c r="K6" s="18">
+        <v>1.5726999999999999E-4</v>
+      </c>
+      <c r="L6" s="18">
+        <v>0</v>
+      </c>
+      <c r="M6" s="18">
+        <v>0</v>
+      </c>
+      <c r="N6" s="18">
+        <v>2.0699999999999998</v>
+      </c>
+      <c r="O6" s="18">
+        <v>2.39</v>
+      </c>
+      <c r="P6" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R6" s="17">
+        <v>5</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T6" s="17">
+        <v>3</v>
+      </c>
+      <c r="U6" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V6" s="17">
+        <v>5.0594E-2</v>
+      </c>
+      <c r="W6" s="17">
+        <v>0.377942893</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A7" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="18">
+        <v>1.0980000000000001</v>
+      </c>
+      <c r="D7" s="18">
+        <v>2.0550000000000002</v>
+      </c>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18">
+        <v>2.0550000000000002</v>
+      </c>
+      <c r="I7" s="18">
+        <v>0</v>
+      </c>
+      <c r="J7" s="18">
+        <v>0</v>
+      </c>
+      <c r="K7" s="18">
+        <v>1.3422099999999999E-4</v>
+      </c>
+      <c r="L7" s="18">
+        <v>0</v>
+      </c>
+      <c r="M7" s="18">
+        <v>0</v>
+      </c>
+      <c r="N7" s="18">
+        <v>1.97</v>
+      </c>
+      <c r="O7" s="18">
+        <v>2.1800000000000002</v>
+      </c>
+      <c r="P7" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q7" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R7" s="17">
+        <v>5</v>
+      </c>
+      <c r="S7" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T7" s="17">
+        <v>3</v>
+      </c>
+      <c r="U7" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V7" s="17">
+        <v>4.5962000000000003E-2</v>
+      </c>
+      <c r="W7" s="17">
+        <v>0.33645671399999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A8" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C8" s="18">
+        <v>1.51</v>
+      </c>
+      <c r="D8" s="18">
+        <v>0.308</v>
+      </c>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18">
+        <v>0.308</v>
+      </c>
+      <c r="I8" s="18">
+        <v>0</v>
+      </c>
+      <c r="J8" s="18">
+        <v>7.5614127000000003E-2</v>
+      </c>
+      <c r="K8" s="18">
+        <v>1.7982350000000001E-2</v>
+      </c>
+      <c r="L8" s="18">
+        <v>0</v>
+      </c>
+      <c r="M8" s="18">
+        <v>0</v>
+      </c>
+      <c r="N8" s="18">
+        <v>3.4660000000000002</v>
+      </c>
+      <c r="O8" s="18">
+        <v>3.6160000000000001</v>
+      </c>
+      <c r="P8" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R8" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S8" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T8" s="17">
+        <v>30</v>
+      </c>
+      <c r="U8" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="V8" s="17">
+        <v>2.2624999999999999E-2</v>
+      </c>
+      <c r="W8" s="17">
+        <v>0.209333929</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A9" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C9" s="18">
+        <v>1.5109999999999999</v>
+      </c>
+      <c r="D9" s="18">
+        <v>0.308</v>
+      </c>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18">
+        <v>0.308</v>
+      </c>
+      <c r="I9" s="18">
+        <v>0</v>
+      </c>
+      <c r="J9" s="18">
+        <v>4.9087042999999997E-2</v>
+      </c>
+      <c r="K9" s="18">
+        <v>1.38432E-2</v>
+      </c>
+      <c r="L9" s="18">
+        <v>0</v>
+      </c>
+      <c r="M9" s="18">
+        <v>0</v>
+      </c>
+      <c r="N9" s="18">
+        <v>3.1360000000000001</v>
+      </c>
+      <c r="O9" s="18">
+        <v>3.5219999999999998</v>
+      </c>
+      <c r="P9" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q9" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R9" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S9" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T9" s="17">
+        <v>30</v>
+      </c>
+      <c r="U9" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="V9" s="17">
+        <v>2.6009999999999998E-2</v>
+      </c>
+      <c r="W9" s="17">
+        <v>0.22151335699999999</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A10" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C10" s="18">
+        <v>1.4890000000000001</v>
+      </c>
+      <c r="D10" s="18">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18">
+        <v>0.30399999999999999</v>
+      </c>
+      <c r="I10" s="18">
+        <v>0</v>
+      </c>
+      <c r="J10" s="18">
+        <v>6.6037847999999996E-2</v>
+      </c>
+      <c r="K10" s="18">
+        <v>1.602926E-2</v>
+      </c>
+      <c r="L10" s="18">
+        <v>0</v>
+      </c>
+      <c r="M10" s="18">
+        <v>0</v>
+      </c>
+      <c r="N10" s="18">
+        <v>3.161</v>
+      </c>
+      <c r="O10" s="18">
+        <v>3.8239999999999998</v>
+      </c>
+      <c r="P10" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R10" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S10" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T10" s="17">
+        <v>30</v>
+      </c>
+      <c r="U10" s="17" t="s">
+        <v>252</v>
+      </c>
+      <c r="V10" s="17">
+        <v>2.7257E-2</v>
+      </c>
+      <c r="W10" s="17">
+        <v>0.24587221400000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A11" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="17">
+        <v>0.13</v>
+      </c>
+      <c r="C11" s="18">
+        <v>2.0190000000000001</v>
+      </c>
+      <c r="D11" s="18">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18">
+        <v>0.41499999999999998</v>
+      </c>
+      <c r="I11" s="18">
+        <v>0.14387805000000001</v>
+      </c>
+      <c r="J11" s="18">
+        <v>0.23128044</v>
+      </c>
+      <c r="K11" s="18">
+        <v>2.4418572999999999E-2</v>
+      </c>
+      <c r="L11" s="18">
+        <v>7.3894399999999995E-4</v>
+      </c>
+      <c r="M11" s="18">
+        <v>4.2122905000000002E-2</v>
+      </c>
+      <c r="N11" s="18">
+        <v>5.51</v>
+      </c>
+      <c r="O11" s="18">
+        <v>5.2519999999999998</v>
+      </c>
+      <c r="P11" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q11" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R11" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S11" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T11" s="17">
+        <v>30</v>
+      </c>
+      <c r="U11" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V11" s="17">
+        <v>2.6366000000000001E-2</v>
+      </c>
+      <c r="W11" s="17">
+        <v>0.30372450000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A12" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" s="17">
+        <v>0.13</v>
+      </c>
+      <c r="C12" s="18">
+        <v>2.0590000000000002</v>
+      </c>
+      <c r="D12" s="18">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="I12" s="18">
+        <v>0.13916811300000001</v>
+      </c>
+      <c r="J12" s="18">
+        <v>0.22761730999999999</v>
+      </c>
+      <c r="K12" s="18">
+        <v>2.5077986E-2</v>
+      </c>
+      <c r="L12" s="18">
+        <v>2.152588E-3</v>
+      </c>
+      <c r="M12" s="18">
+        <v>3.3899711999999999E-2</v>
+      </c>
+      <c r="N12" s="18">
+        <v>5.3739999999999997</v>
+      </c>
+      <c r="O12" s="18">
+        <v>4.5460000000000003</v>
+      </c>
+      <c r="P12" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q12" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R12" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S12" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T12" s="17">
+        <v>30</v>
+      </c>
+      <c r="U12" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V12" s="17">
+        <v>2.5831E-2</v>
+      </c>
+      <c r="W12" s="17">
+        <v>0.25690982099999998</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A13" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" s="17">
+        <v>0.13</v>
+      </c>
+      <c r="C13" s="18">
+        <v>2.1349999999999998</v>
+      </c>
+      <c r="D13" s="18">
+        <v>0.438</v>
+      </c>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18">
+        <v>0.438</v>
+      </c>
+      <c r="I13" s="18">
+        <v>0.13267562499999999</v>
+      </c>
+      <c r="J13" s="18">
+        <v>0.25727792100000002</v>
+      </c>
+      <c r="K13" s="18">
+        <v>2.6121129999999999E-2</v>
+      </c>
+      <c r="L13" s="18">
+        <v>0</v>
+      </c>
+      <c r="M13" s="18">
+        <v>4.1071206999999998E-2</v>
+      </c>
+      <c r="N13" s="18">
+        <v>5.3019999999999996</v>
+      </c>
+      <c r="O13" s="18">
+        <v>5.07</v>
+      </c>
+      <c r="P13" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q13" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R13" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S13" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T13" s="17">
+        <v>30</v>
+      </c>
+      <c r="U13" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V13" s="17">
+        <v>2.5297E-2</v>
+      </c>
+      <c r="W13" s="17">
+        <v>0.26642500000000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="17">
+        <v>0.18</v>
+      </c>
+      <c r="C14" s="18">
+        <v>3.266</v>
+      </c>
+      <c r="D14" s="18">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18">
+        <v>0.66900000000000004</v>
+      </c>
+      <c r="I14" s="18">
+        <v>1.2813869950000001</v>
+      </c>
+      <c r="J14" s="18">
+        <v>0.18048138799999999</v>
+      </c>
+      <c r="K14" s="18">
+        <v>3.2745818000000003E-2</v>
+      </c>
+      <c r="L14" s="18">
+        <v>0</v>
+      </c>
+      <c r="M14" s="18">
+        <v>5.6452840000000004E-3</v>
+      </c>
+      <c r="N14" s="18">
+        <v>7.2619999999999996</v>
+      </c>
+      <c r="O14" s="18">
+        <v>5.42</v>
+      </c>
+      <c r="P14" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q14" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R14" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S14" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T14" s="17">
+        <v>30</v>
+      </c>
+      <c r="U14" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V14" s="17">
+        <v>3.9014E-2</v>
+      </c>
+      <c r="W14" s="17">
+        <v>0.28926142900000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="17">
+        <v>0.18</v>
+      </c>
+      <c r="C15" s="18">
+        <v>3.202</v>
+      </c>
+      <c r="D15" s="18">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18">
+        <v>0.65900000000000003</v>
+      </c>
+      <c r="I15" s="18">
+        <v>1.4870797280000001</v>
+      </c>
+      <c r="J15" s="18">
+        <v>0.41515672300000001</v>
+      </c>
+      <c r="K15" s="18">
+        <v>3.1272250000000001E-2</v>
+      </c>
+      <c r="L15" s="18">
+        <v>2.6969479999999998E-3</v>
+      </c>
+      <c r="M15" s="18">
+        <v>1.6418242E-2</v>
+      </c>
+      <c r="N15" s="18">
+        <v>7.3049999999999997</v>
+      </c>
+      <c r="O15" s="18">
+        <v>6.0170000000000003</v>
+      </c>
+      <c r="P15" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q15" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R15" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S15" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T15" s="17">
+        <v>30</v>
+      </c>
+      <c r="U15" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V15" s="17">
+        <v>3.8657999999999998E-2</v>
+      </c>
+      <c r="W15" s="17">
+        <v>0.28202989299999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="17">
+        <v>0.18</v>
+      </c>
+      <c r="C16" s="18">
+        <v>2.83</v>
+      </c>
+      <c r="D16" s="18">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="I16" s="18">
+        <v>1.069367508</v>
+      </c>
+      <c r="J16" s="18">
+        <v>0.18424942899999999</v>
+      </c>
+      <c r="K16" s="18">
+        <v>2.652065E-2</v>
+      </c>
+      <c r="L16" s="18">
+        <v>0</v>
+      </c>
+      <c r="M16" s="18">
+        <v>1.5674206999999999E-2</v>
+      </c>
+      <c r="N16" s="18">
+        <v>6.2510000000000003</v>
+      </c>
+      <c r="O16" s="18">
+        <v>5.2640000000000002</v>
+      </c>
+      <c r="P16" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q16" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R16" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S16" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T16" s="17">
+        <v>30</v>
+      </c>
+      <c r="U16" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V16" s="17">
+        <v>3.7945E-2</v>
+      </c>
+      <c r="W16" s="17">
+        <v>0.288119607</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A17" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="C17" s="18">
+        <v>7.9909999999999997</v>
+      </c>
+      <c r="D17" s="18">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18">
+        <v>1.6479999999999999</v>
+      </c>
+      <c r="I17" s="18">
+        <v>7.0441347099999998</v>
+      </c>
+      <c r="J17" s="18">
+        <v>0.31251037799999998</v>
+      </c>
+      <c r="K17" s="18">
+        <v>5.1692219999999997E-2</v>
+      </c>
+      <c r="L17" s="18">
+        <v>1.1339925000000001E-2</v>
+      </c>
+      <c r="M17" s="18">
+        <v>0</v>
+      </c>
+      <c r="N17" s="18">
+        <v>14.086</v>
+      </c>
+      <c r="O17" s="18">
+        <v>8.3010000000000002</v>
+      </c>
+      <c r="P17" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q17" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R17" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S17" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T17" s="17">
+        <v>30</v>
+      </c>
+      <c r="U17" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V17" s="17">
+        <v>4.7031000000000003E-2</v>
+      </c>
+      <c r="W17" s="17">
+        <v>0.42247392900000003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A18" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="C18" s="18">
+        <v>8.2759999999999998</v>
+      </c>
+      <c r="D18" s="18">
+        <v>1.6950000000000001</v>
+      </c>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18">
+        <v>1.6950000000000001</v>
+      </c>
+      <c r="I18" s="18">
+        <v>6.6847254490000001</v>
+      </c>
+      <c r="J18" s="18">
+        <v>0.27229536399999998</v>
+      </c>
+      <c r="K18" s="18">
+        <v>4.4478275999999997E-2</v>
+      </c>
+      <c r="L18" s="18">
+        <v>3.4668667E-2</v>
+      </c>
+      <c r="M18" s="18">
+        <v>0</v>
+      </c>
+      <c r="N18" s="18">
+        <v>15.111000000000001</v>
+      </c>
+      <c r="O18" s="18">
+        <v>8.3870000000000005</v>
+      </c>
+      <c r="P18" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q18" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R18" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S18" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T18" s="17">
+        <v>30</v>
+      </c>
+      <c r="U18" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V18" s="17">
+        <v>4.5606000000000001E-2</v>
+      </c>
+      <c r="W18" s="17">
+        <v>0.42133210700000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" s="17">
+        <v>0.3</v>
+      </c>
+      <c r="C19" s="18">
+        <v>8.9320000000000004</v>
+      </c>
+      <c r="D19" s="18">
+        <v>1.8660000000000001</v>
+      </c>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18">
+        <v>1.8660000000000001</v>
+      </c>
+      <c r="I19" s="18">
+        <v>8.2124218889999998</v>
+      </c>
+      <c r="J19" s="18">
+        <v>0.61718923199999998</v>
+      </c>
+      <c r="K19" s="18">
+        <v>6.4337543999999997E-2</v>
+      </c>
+      <c r="L19" s="18">
+        <v>2.9481279999999999E-2</v>
+      </c>
+      <c r="M19" s="18">
+        <v>0</v>
+      </c>
+      <c r="N19" s="18">
+        <v>16.956</v>
+      </c>
+      <c r="O19" s="18">
+        <v>9.34</v>
+      </c>
+      <c r="P19" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q19" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R19" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S19" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T19" s="17">
+        <v>30</v>
+      </c>
+      <c r="U19" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V19" s="17">
+        <v>5.2019000000000003E-2</v>
+      </c>
+      <c r="W19" s="17">
+        <v>0.39963749999999998</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="C20" s="18">
+        <v>12.936999999999999</v>
+      </c>
+      <c r="D20" s="18">
+        <v>2.7120000000000002</v>
+      </c>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18">
+        <v>2.7120000000000002</v>
+      </c>
+      <c r="I20" s="18">
+        <v>11.927306959999999</v>
+      </c>
+      <c r="J20" s="18">
+        <v>0.47269426599999997</v>
+      </c>
+      <c r="K20" s="18">
+        <v>8.9757966999999994E-2</v>
+      </c>
+      <c r="L20" s="18">
+        <v>3.5944587E-2</v>
+      </c>
+      <c r="M20" s="18">
+        <v>0</v>
+      </c>
+      <c r="N20" s="18">
+        <v>20.902000000000001</v>
+      </c>
+      <c r="O20" s="18">
+        <v>12.682</v>
+      </c>
+      <c r="P20" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q20" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R20" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S20" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T20" s="17">
+        <v>30</v>
+      </c>
+      <c r="U20" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V20" s="17">
+        <v>7.3219000000000006E-2</v>
+      </c>
+      <c r="W20" s="17">
+        <v>0.48415467400000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="C21" s="18">
+        <v>13.23</v>
+      </c>
+      <c r="D21" s="18">
+        <v>2.786</v>
+      </c>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18">
+        <v>2.786</v>
+      </c>
+      <c r="I21" s="18">
+        <v>12.12470377</v>
+      </c>
+      <c r="J21" s="18">
+        <v>0.63692599999999999</v>
+      </c>
+      <c r="K21" s="18">
+        <v>0.104193063</v>
+      </c>
+      <c r="L21" s="18">
+        <v>3.3770889999999998E-2</v>
+      </c>
+      <c r="M21" s="18">
+        <v>0</v>
+      </c>
+      <c r="N21" s="18">
+        <v>21.082999999999998</v>
+      </c>
+      <c r="O21" s="18">
+        <v>12.353999999999999</v>
+      </c>
+      <c r="P21" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q21" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R21" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S21" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T21" s="17">
+        <v>30</v>
+      </c>
+      <c r="U21" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V21" s="17">
+        <v>7.0545999999999998E-2</v>
+      </c>
+      <c r="W21" s="17">
+        <v>0.48992198300000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A22" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="C22" s="18">
+        <v>13.096</v>
+      </c>
+      <c r="D22" s="18">
+        <v>2.742</v>
+      </c>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18">
+        <v>2.742</v>
+      </c>
+      <c r="I22" s="18">
+        <v>11.84780602</v>
+      </c>
+      <c r="J22" s="18">
+        <v>0.47734259699999998</v>
+      </c>
+      <c r="K22" s="18">
+        <v>9.1823417000000004E-2</v>
+      </c>
+      <c r="L22" s="18">
+        <v>0</v>
+      </c>
+      <c r="M22" s="18">
+        <v>0</v>
+      </c>
+      <c r="N22" s="18">
+        <v>21.097999999999999</v>
+      </c>
+      <c r="O22" s="18">
+        <v>12.977</v>
+      </c>
+      <c r="P22" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q22" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="R22" s="17">
+        <v>0.5</v>
+      </c>
+      <c r="S22" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T22" s="17">
+        <v>30</v>
+      </c>
+      <c r="U22" s="17" t="s">
+        <v>249</v>
+      </c>
+      <c r="V22" s="17">
+        <v>8.8717000000000004E-2</v>
+      </c>
+      <c r="W22" s="17">
+        <v>0.50886425499999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A23" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C23" s="18">
+        <v>0.82699999999999996</v>
+      </c>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18">
+        <v>0.747</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18">
+        <v>1.4930000000000001</v>
+      </c>
+      <c r="I23" s="18">
+        <v>0</v>
+      </c>
+      <c r="J23" s="18">
+        <v>0</v>
+      </c>
+      <c r="K23" s="18">
+        <v>8.7561730000000008E-3</v>
+      </c>
+      <c r="L23" s="18">
+        <v>0</v>
+      </c>
+      <c r="M23" s="18">
+        <v>0</v>
+      </c>
+      <c r="N23" s="18">
+        <v>2.7690000000000001</v>
+      </c>
+      <c r="O23" s="18">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="P23" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q23" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="R23" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="S23" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T23" s="17">
+        <v>5</v>
+      </c>
+      <c r="U23" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V23" s="17">
+        <v>7.1259000000000003E-2</v>
+      </c>
+      <c r="W23" s="17">
+        <v>0.49783414300000001</v>
+      </c>
+      <c r="X23" s="17" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A24" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C24" s="18">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18">
+        <v>1.423</v>
+      </c>
+      <c r="I24" s="18">
+        <v>0</v>
+      </c>
+      <c r="J24" s="18">
+        <v>0</v>
+      </c>
+      <c r="K24" s="18">
+        <v>5.5182690000000001E-3</v>
+      </c>
+      <c r="L24" s="18">
+        <v>0</v>
+      </c>
+      <c r="M24" s="18">
+        <v>0</v>
+      </c>
+      <c r="N24" s="18">
+        <v>2.7170000000000001</v>
+      </c>
+      <c r="O24" s="18">
+        <v>2.3530000000000002</v>
+      </c>
+      <c r="P24" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q24" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="R24" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="S24" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T24" s="17">
+        <v>5</v>
+      </c>
+      <c r="U24" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V24" s="17">
+        <v>5.8789000000000001E-2</v>
+      </c>
+      <c r="W24" s="17">
+        <v>0.58385135700000002</v>
+      </c>
+      <c r="X24" s="17" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A25" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C25" s="18">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18">
+        <v>1.3819999999999999</v>
+      </c>
+      <c r="I25" s="18">
+        <v>0</v>
+      </c>
+      <c r="J25" s="18">
+        <v>0</v>
+      </c>
+      <c r="K25" s="18">
+        <v>1.9902549999999998E-3</v>
+      </c>
+      <c r="L25" s="18">
+        <v>0</v>
+      </c>
+      <c r="M25" s="18">
+        <v>0</v>
+      </c>
+      <c r="N25" s="18">
+        <v>2.5739999999999998</v>
+      </c>
+      <c r="O25" s="18">
+        <v>2.25</v>
+      </c>
+      <c r="P25" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q25" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="R25" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="S25" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T25" s="17">
+        <v>5</v>
+      </c>
+      <c r="U25" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V25" s="17">
+        <v>6.4132999999999996E-2</v>
+      </c>
+      <c r="W25" s="17">
+        <v>0.59412774999999995</v>
+      </c>
+      <c r="X25" s="17" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A26" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C26" s="18">
+        <v>0.80700000000000005</v>
+      </c>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18">
+        <v>4.92</v>
+      </c>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18">
+        <v>9.8390000000000004</v>
+      </c>
+      <c r="I26" s="18">
+        <v>0</v>
+      </c>
+      <c r="J26" s="18">
+        <v>0</v>
+      </c>
+      <c r="K26" s="18">
+        <v>3.9436786000000001E-2</v>
+      </c>
+      <c r="L26" s="18">
+        <v>0</v>
+      </c>
+      <c r="M26" s="18">
+        <v>1.3630471999999999E-2</v>
+      </c>
+      <c r="N26" s="18">
+        <v>3.032</v>
+      </c>
+      <c r="O26" s="18">
+        <v>1.7749999999999999</v>
+      </c>
+      <c r="P26" s="19">
+        <v>1.21</v>
+      </c>
+      <c r="Q26" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="R26" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="S26" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T26" s="17">
+        <v>3</v>
+      </c>
+      <c r="U26" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V26" s="17">
+        <v>5.5581999999999999E-2</v>
+      </c>
+      <c r="W26" s="17">
+        <v>0.510013571</v>
+      </c>
+      <c r="X26" s="17" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C27" s="18">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="D27" s="18"/>
+      <c r="E27" s="18">
+        <v>3.9620000000000002</v>
+      </c>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18">
+        <v>7.9240000000000004</v>
+      </c>
+      <c r="I27" s="18">
+        <v>0</v>
+      </c>
+      <c r="J27" s="18">
+        <v>0</v>
+      </c>
+      <c r="K27" s="18">
+        <v>3.0460814999999999E-2</v>
+      </c>
+      <c r="L27" s="18">
+        <v>0</v>
+      </c>
+      <c r="M27" s="18">
+        <v>9.5061450000000006E-3</v>
+      </c>
+      <c r="N27" s="18">
+        <v>1.9590000000000001</v>
+      </c>
+      <c r="O27" s="18">
+        <v>1.623</v>
+      </c>
+      <c r="P27" s="19">
+        <v>1.21</v>
+      </c>
+      <c r="Q27" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="R27" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="S27" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T27" s="17">
+        <v>3</v>
+      </c>
+      <c r="U27" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V27" s="17">
+        <v>5.4869000000000001E-2</v>
+      </c>
+      <c r="W27" s="17">
+        <v>0.29420932100000002</v>
+      </c>
+      <c r="X27" s="17" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A28" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C28" s="18">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="D28" s="18"/>
+      <c r="E28" s="18">
+        <v>4.6159999999999997</v>
+      </c>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18">
+        <v>9.2319999999999993</v>
+      </c>
+      <c r="I28" s="18">
+        <v>0</v>
+      </c>
+      <c r="J28" s="18">
+        <v>0</v>
+      </c>
+      <c r="K28" s="18">
+        <v>2.5119712999999998E-2</v>
+      </c>
+      <c r="L28" s="18">
+        <v>0</v>
+      </c>
+      <c r="M28" s="18">
+        <v>0</v>
+      </c>
+      <c r="N28" s="18">
+        <v>2.569</v>
+      </c>
+      <c r="O28" s="18">
+        <v>1.2909999999999999</v>
+      </c>
+      <c r="P28" s="19">
+        <v>1.21</v>
+      </c>
+      <c r="Q28" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="R28" s="17">
+        <v>5.53</v>
+      </c>
+      <c r="S28" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T28" s="17">
+        <v>3</v>
+      </c>
+      <c r="U28" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V28" s="17">
+        <v>5.1663000000000001E-2</v>
+      </c>
+      <c r="W28" s="17">
+        <v>0.358912536</v>
+      </c>
+      <c r="X28" s="17" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A29" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C29" s="18">
+        <v>1.381</v>
+      </c>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18">
+        <v>0.158</v>
+      </c>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18">
+        <v>0.317</v>
+      </c>
+      <c r="I29" s="18">
+        <v>1.8073279000000001E-2</v>
+      </c>
+      <c r="J29" s="18">
+        <v>7.8381013999999999E-2</v>
+      </c>
+      <c r="K29" s="18">
+        <v>0.86713414300000002</v>
+      </c>
+      <c r="L29" s="18">
+        <v>5.4564440000000004E-3</v>
+      </c>
+      <c r="M29" s="18">
+        <v>4.6616212999999997E-2</v>
+      </c>
+      <c r="N29" s="18">
+        <v>4.3209999999999997</v>
+      </c>
+      <c r="O29" s="18">
+        <v>3.883</v>
+      </c>
+      <c r="P29" s="19">
+        <v>6.87</v>
+      </c>
+      <c r="Q29" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="R29" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="S29" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T29" s="17">
+        <v>30</v>
+      </c>
+      <c r="U29" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V29" s="17">
+        <v>2.6366000000000001E-2</v>
+      </c>
+      <c r="W29" s="17">
+        <v>0.20552785700000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A30" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C30" s="18">
+        <v>1.2589999999999999</v>
+      </c>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="I30" s="18">
+        <v>0</v>
+      </c>
+      <c r="J30" s="18">
+        <v>3.4333113999999998E-2</v>
+      </c>
+      <c r="K30" s="18">
+        <v>0.69158415699999998</v>
+      </c>
+      <c r="L30" s="18">
+        <v>0</v>
+      </c>
+      <c r="M30" s="18">
+        <v>4.5041784000000001E-2</v>
+      </c>
+      <c r="N30" s="18">
+        <v>3.93</v>
+      </c>
+      <c r="O30" s="18">
+        <v>3.3959999999999999</v>
+      </c>
+      <c r="P30" s="19">
+        <v>6.87</v>
+      </c>
+      <c r="Q30" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="R30" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="S30" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T30" s="17">
+        <v>30</v>
+      </c>
+      <c r="U30" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V30" s="17">
+        <v>2.2268E-2</v>
+      </c>
+      <c r="W30" s="17">
+        <v>0.35282282100000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C31" s="18">
+        <v>1.3</v>
+      </c>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18">
+        <v>0.14899999999999999</v>
+      </c>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18">
+        <v>0.29799999999999999</v>
+      </c>
+      <c r="I31" s="18">
+        <v>0</v>
+      </c>
+      <c r="J31" s="18">
+        <v>7.6426068999999999E-2</v>
+      </c>
+      <c r="K31" s="18">
+        <v>0.84262339500000005</v>
+      </c>
+      <c r="L31" s="18">
+        <v>5.663179E-3</v>
+      </c>
+      <c r="M31" s="18">
+        <v>4.1991897E-2</v>
+      </c>
+      <c r="N31" s="18">
+        <v>4.077</v>
+      </c>
+      <c r="O31" s="18">
+        <v>3.3340000000000001</v>
+      </c>
+      <c r="P31" s="19">
+        <v>6.87</v>
+      </c>
+      <c r="Q31" s="17" t="s">
+        <v>253</v>
+      </c>
+      <c r="R31" s="17">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="S31" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T31" s="17">
+        <v>30</v>
+      </c>
+      <c r="U31" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V31" s="17">
+        <v>1.7815000000000001E-2</v>
+      </c>
+      <c r="W31" s="17">
+        <v>0.36195739300000002</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A32" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C32" s="18">
+        <v>1.4850000000000001</v>
+      </c>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18">
+        <v>2.8620000000000001</v>
+      </c>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18">
+        <v>2.8620000000000001</v>
+      </c>
+      <c r="I32" s="18">
+        <v>0</v>
+      </c>
+      <c r="J32" s="18">
+        <v>0</v>
+      </c>
+      <c r="K32" s="18">
+        <v>6.3162172000000003E-2</v>
+      </c>
+      <c r="L32" s="18">
+        <v>0</v>
+      </c>
+      <c r="M32" s="18">
+        <v>0</v>
+      </c>
+      <c r="N32" s="18">
+        <v>5.7110000000000003</v>
+      </c>
+      <c r="O32" s="18">
+        <v>5.6040000000000001</v>
+      </c>
+      <c r="P32" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q32" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="R32" s="17">
+        <v>12.35</v>
+      </c>
+      <c r="S32" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T32" s="17">
+        <v>3</v>
+      </c>
+      <c r="U32" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V32" s="17">
+        <v>1.9595999999999999E-2</v>
+      </c>
+      <c r="W32" s="17">
+        <v>0.425138179</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A33" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C33" s="18">
+        <v>1.6</v>
+      </c>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18">
+        <v>3.0840000000000001</v>
+      </c>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18">
+        <v>3.0840000000000001</v>
+      </c>
+      <c r="I33" s="18">
+        <v>0</v>
+      </c>
+      <c r="J33" s="18">
+        <v>0</v>
+      </c>
+      <c r="K33" s="18">
+        <v>7.4209667000000007E-2</v>
+      </c>
+      <c r="L33" s="18">
+        <v>0</v>
+      </c>
+      <c r="M33" s="18">
+        <v>0</v>
+      </c>
+      <c r="N33" s="18">
+        <v>6.0389999999999997</v>
+      </c>
+      <c r="O33" s="18">
+        <v>5.8689999999999998</v>
+      </c>
+      <c r="P33" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q33" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="R33" s="17">
+        <v>12.35</v>
+      </c>
+      <c r="S33" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T33" s="17">
+        <v>3</v>
+      </c>
+      <c r="U33" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V33" s="17">
+        <v>2.0309000000000001E-2</v>
+      </c>
+      <c r="W33" s="17">
+        <v>0.52028996400000005</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A34" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C34" s="18">
+        <v>1.4350000000000001</v>
+      </c>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18">
+        <v>2.7629999999999999</v>
+      </c>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18">
+        <v>2.7629999999999999</v>
+      </c>
+      <c r="I34" s="18">
+        <v>0</v>
+      </c>
+      <c r="J34" s="18">
+        <v>0</v>
+      </c>
+      <c r="K34" s="18">
+        <v>7.4921513999999995E-2</v>
+      </c>
+      <c r="L34" s="18">
+        <v>0</v>
+      </c>
+      <c r="M34" s="18">
+        <v>0</v>
+      </c>
+      <c r="N34" s="18">
+        <v>5.32</v>
+      </c>
+      <c r="O34" s="18">
+        <v>5.0789999999999997</v>
+      </c>
+      <c r="P34" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q34" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="R34" s="17">
+        <v>12.35</v>
+      </c>
+      <c r="S34" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T34" s="17">
+        <v>3</v>
+      </c>
+      <c r="U34" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V34" s="17">
+        <v>1.8171E-2</v>
+      </c>
+      <c r="W34" s="17">
+        <v>0.452161286</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A35" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C35" s="18">
+        <v>1.6779999999999999</v>
+      </c>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="I35" s="18">
+        <v>0</v>
+      </c>
+      <c r="J35" s="18">
+        <v>0</v>
+      </c>
+      <c r="K35" s="18">
+        <v>0.27117874199999997</v>
+      </c>
+      <c r="L35" s="18">
+        <v>0</v>
+      </c>
+      <c r="M35" s="18">
+        <v>0</v>
+      </c>
+      <c r="N35" s="18">
+        <v>5.7240000000000002</v>
+      </c>
+      <c r="O35" s="18">
+        <v>5.9080000000000004</v>
+      </c>
+      <c r="P35" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q35" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="R35" s="17">
+        <v>1.24</v>
+      </c>
+      <c r="S35" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T35" s="17">
+        <v>30</v>
+      </c>
+      <c r="U35" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V35" s="17">
+        <v>2.3337E-2</v>
+      </c>
+      <c r="W35" s="17">
+        <v>0.41790664300000002</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A36" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C36" s="18">
+        <v>1.6930000000000001</v>
+      </c>
+      <c r="D36" s="18"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="18">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="G36" s="18"/>
+      <c r="H36" s="18">
+        <v>0.33700000000000002</v>
+      </c>
+      <c r="I36" s="18">
+        <v>0</v>
+      </c>
+      <c r="J36" s="18">
+        <v>0</v>
+      </c>
+      <c r="K36" s="18">
+        <v>0.30716928599999999</v>
+      </c>
+      <c r="L36" s="18">
+        <v>0</v>
+      </c>
+      <c r="M36" s="18">
+        <v>0</v>
+      </c>
+      <c r="N36" s="18">
+        <v>5.9720000000000004</v>
+      </c>
+      <c r="O36" s="18">
+        <v>5.29</v>
+      </c>
+      <c r="P36" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q36" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="R36" s="17">
+        <v>1.24</v>
+      </c>
+      <c r="S36" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T36" s="17">
+        <v>30</v>
+      </c>
+      <c r="U36" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V36" s="17">
+        <v>2.4941000000000001E-2</v>
+      </c>
+      <c r="W36" s="17">
+        <v>0.37870410700000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A37" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C37" s="18">
+        <v>1.647</v>
+      </c>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="18">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="G37" s="18"/>
+      <c r="H37" s="18">
+        <v>0.32700000000000001</v>
+      </c>
+      <c r="I37" s="18">
+        <v>0</v>
+      </c>
+      <c r="J37" s="18">
+        <v>0</v>
+      </c>
+      <c r="K37" s="18">
+        <v>0.20397084300000001</v>
+      </c>
+      <c r="L37" s="18">
+        <v>0</v>
+      </c>
+      <c r="M37" s="18">
+        <v>0</v>
+      </c>
+      <c r="N37" s="18">
+        <v>6.1310000000000002</v>
+      </c>
+      <c r="O37" s="18">
+        <v>5.69</v>
+      </c>
+      <c r="P37" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q37" s="17" t="s">
+        <v>256</v>
+      </c>
+      <c r="R37" s="17">
+        <v>1.24</v>
+      </c>
+      <c r="S37" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T37" s="17">
+        <v>30</v>
+      </c>
+      <c r="U37" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V37" s="17">
+        <v>2.4406000000000001E-2</v>
+      </c>
+      <c r="W37" s="17">
+        <v>0.39887628600000002</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C38" s="18">
+        <v>1.4790000000000001</v>
+      </c>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18">
+        <v>2.919</v>
+      </c>
+      <c r="H38" s="18">
+        <v>2.919</v>
+      </c>
+      <c r="I38" s="18">
+        <v>6.4434642E-2</v>
+      </c>
+      <c r="J38" s="18">
+        <v>0</v>
+      </c>
+      <c r="K38" s="18">
+        <v>0.16559933199999999</v>
+      </c>
+      <c r="L38" s="18">
+        <v>0</v>
+      </c>
+      <c r="M38" s="18">
+        <v>4.8736990000000004E-3</v>
+      </c>
+      <c r="N38" s="18">
+        <v>4.7869999999999999</v>
+      </c>
+      <c r="O38" s="18">
+        <v>4.5609999999999999</v>
+      </c>
+      <c r="P38" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q38" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="R38" s="17">
+        <v>9.81</v>
+      </c>
+      <c r="S38" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T38" s="17">
+        <v>3</v>
+      </c>
+      <c r="U38" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V38" s="17">
+        <v>2.9215999999999999E-2</v>
+      </c>
+      <c r="W38" s="17">
+        <v>0.32085182099999998</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C39" s="18">
+        <v>1.633</v>
+      </c>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="H39" s="18">
+        <v>3.2</v>
+      </c>
+      <c r="I39" s="18">
+        <v>0</v>
+      </c>
+      <c r="J39" s="18">
+        <v>0</v>
+      </c>
+      <c r="K39" s="18">
+        <v>0.156217087</v>
+      </c>
+      <c r="L39" s="18">
+        <v>0</v>
+      </c>
+      <c r="M39" s="18">
+        <v>0</v>
+      </c>
+      <c r="N39" s="18">
+        <v>5.1379999999999999</v>
+      </c>
+      <c r="O39" s="18">
+        <v>4.9089999999999998</v>
+      </c>
+      <c r="P39" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q39" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="R39" s="17">
+        <v>9.81</v>
+      </c>
+      <c r="S39" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T39" s="17">
+        <v>3</v>
+      </c>
+      <c r="U39" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V39" s="17">
+        <v>3.4738999999999999E-2</v>
+      </c>
+      <c r="W39" s="17">
+        <v>0.41866785699999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C40" s="18">
+        <v>1.571</v>
+      </c>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18">
+        <v>3.0830000000000002</v>
+      </c>
+      <c r="H40" s="18">
+        <v>3.0830000000000002</v>
+      </c>
+      <c r="I40" s="18">
+        <v>6.4504826000000001E-2</v>
+      </c>
+      <c r="J40" s="18">
+        <v>0</v>
+      </c>
+      <c r="K40" s="18">
+        <v>0.15037355499999999</v>
+      </c>
+      <c r="L40" s="18">
+        <v>0</v>
+      </c>
+      <c r="M40" s="18">
+        <v>5.596462E-3</v>
+      </c>
+      <c r="N40" s="18">
+        <v>4.9610000000000003</v>
+      </c>
+      <c r="O40" s="18">
+        <v>4.5490000000000004</v>
+      </c>
+      <c r="P40" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q40" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="R40" s="17">
+        <v>9.81</v>
+      </c>
+      <c r="S40" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="T40" s="17">
+        <v>3</v>
+      </c>
+      <c r="U40" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V40" s="17">
+        <v>3.0641000000000002E-2</v>
+      </c>
+      <c r="W40" s="17">
+        <v>0.33150882100000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C41" s="18">
+        <v>1.4510000000000001</v>
+      </c>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="H41" s="18">
+        <v>0.29199999999999998</v>
+      </c>
+      <c r="I41" s="18">
+        <v>0.16597783599999999</v>
+      </c>
+      <c r="J41" s="18">
+        <v>6.6479359000000002E-2</v>
+      </c>
+      <c r="K41" s="18">
+        <v>0.60819290000000004</v>
+      </c>
+      <c r="L41" s="18">
+        <v>0</v>
+      </c>
+      <c r="M41" s="18">
+        <v>2.5725250000000002E-2</v>
+      </c>
+      <c r="N41" s="18">
+        <v>4.18</v>
+      </c>
+      <c r="O41" s="18">
+        <v>4.0129999999999999</v>
+      </c>
+      <c r="P41" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q41" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="R41" s="17">
+        <v>0.98</v>
+      </c>
+      <c r="S41" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T41" s="17">
+        <v>30</v>
+      </c>
+      <c r="U41" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V41" s="17">
+        <v>2.4761999999999999E-2</v>
+      </c>
+      <c r="W41" s="17">
+        <v>0.43998185699999998</v>
+      </c>
+    </row>
+    <row r="42" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C42" s="18">
+        <v>1.7090000000000001</v>
+      </c>
+      <c r="D42" s="18"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="18"/>
+      <c r="G42" s="18">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="H42" s="18">
+        <v>0.33900000000000002</v>
+      </c>
+      <c r="I42" s="18">
+        <v>6.0174350000000001E-2</v>
+      </c>
+      <c r="J42" s="18">
+        <v>7.8079274000000004E-2</v>
+      </c>
+      <c r="K42" s="18">
+        <v>0.66867871400000001</v>
+      </c>
+      <c r="L42" s="18">
+        <v>0</v>
+      </c>
+      <c r="M42" s="18">
+        <v>3.5868012999999997E-2</v>
+      </c>
+      <c r="N42" s="18">
+        <v>4.9020000000000001</v>
+      </c>
+      <c r="O42" s="18">
+        <v>4.45</v>
+      </c>
+      <c r="P42" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q42" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="R42" s="17">
+        <v>0.98</v>
+      </c>
+      <c r="S42" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T42" s="17">
+        <v>30</v>
+      </c>
+      <c r="U42" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V42" s="17">
+        <v>2.1912000000000001E-2</v>
+      </c>
+      <c r="W42" s="17">
+        <v>0.448355214</v>
+      </c>
+    </row>
+    <row r="43" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" s="17">
+        <v>0.1</v>
+      </c>
+      <c r="C43" s="18">
+        <v>1.6220000000000001</v>
+      </c>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="H43" s="18">
+        <v>0.32900000000000001</v>
+      </c>
+      <c r="I43" s="18">
+        <v>0.18362290100000001</v>
+      </c>
+      <c r="J43" s="18">
+        <v>0.16825845</v>
+      </c>
+      <c r="K43" s="18">
+        <v>0.92271634599999997</v>
+      </c>
+      <c r="L43" s="18">
+        <v>0</v>
+      </c>
+      <c r="M43" s="18">
+        <v>4.8272586999999999E-2</v>
+      </c>
+      <c r="N43" s="18">
+        <v>4.5620000000000003</v>
+      </c>
+      <c r="O43" s="18">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="P43" s="19">
+        <v>7.5</v>
+      </c>
+      <c r="Q43" s="17" t="s">
+        <v>257</v>
+      </c>
+      <c r="R43" s="17">
+        <v>0.98</v>
+      </c>
+      <c r="S43" s="17" t="s">
+        <v>248</v>
+      </c>
+      <c r="T43" s="17">
+        <v>30</v>
+      </c>
+      <c r="U43" s="17" t="s">
+        <v>251</v>
+      </c>
+      <c r="V43" s="17">
+        <v>2.4761999999999999E-2</v>
+      </c>
+      <c r="W43" s="17">
+        <v>0.42361575000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>